--- a/TICKET ONEWAY.xlsx
+++ b/TICKET ONEWAY.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Train\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9641D171-57DB-41E1-825C-3E20F40AF580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="20490" windowHeight="7500" activeTab="2"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="delhi to haridwar" sheetId="7" r:id="rId1"/>
@@ -14,8 +20,6 @@
     <sheet name="udaipur to ajmer" sheetId="8" r:id="rId5"/>
     <sheet name="Sheet1" sheetId="1" r:id="rId6"/>
     <sheet name="Asarwa to udaipur" sheetId="4" r:id="rId7"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId8"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'ajmer to haridwar'!$A$5:$N$5</definedName>
@@ -1084,17 +1088,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="180" formatCode="dd/mmm"/>
-    <numFmt numFmtId="181" formatCode="dd/mm/yyyy\ hh:mm"/>
-    <numFmt numFmtId="182" formatCode="dd/mm/yyyy"/>
-  </numFmts>
-  <fonts count="23">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1125,152 +1120,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1279,7 +1130,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399945066682943"/>
+        <fgColor theme="9" tint="0.39991454817346722"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1289,194 +1140,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="15">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1562,253 +1227,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1822,35 +1245,20 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="181" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1863,7 +1271,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1879,9 +1287,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1893,7 +1301,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="182" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1902,68 +1310,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="180" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -2248,29 +1630,29 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:N24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="32.1428571428571" customWidth="1"/>
+    <col min="3" max="3" width="32.140625" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="7" max="7" width="15.2857142857143" customWidth="1"/>
-    <col min="8" max="8" width="9.71428571428571" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
     <col min="10" max="10" width="24" customWidth="1"/>
-    <col min="11" max="11" width="0.285714285714286" customWidth="1"/>
+    <col min="11" max="11" width="0.28515625" customWidth="1"/>
     <col min="12" max="12" width="9" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="10.1428571428571" customWidth="1"/>
-    <col min="14" max="14" width="9.71428571428571" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="26.25" spans="1:14">
+    <row r="2" spans="1:14" ht="26.25">
       <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
@@ -2279,22 +1661,22 @@
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="21"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="22"/>
-      <c r="I3" s="22"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="22"/>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-    </row>
-    <row r="4" ht="26.25" spans="1:14">
+      <c r="A3" s="47"/>
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+      <c r="M3" s="48"/>
+      <c r="N3" s="48"/>
+    </row>
+    <row r="4" spans="1:14" ht="26.25">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
@@ -2360,7 +1742,7 @@
       </c>
       <c r="N5" s="5"/>
     </row>
-    <row r="6" ht="19.9" customHeight="1" spans="1:14">
+    <row r="6" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A6" s="14">
         <v>1</v>
       </c>
@@ -2379,28 +1761,28 @@
       <c r="F6" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="40">
+      <c r="G6" s="35">
         <v>46292</v>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="36">
         <v>0.211805555555556</v>
       </c>
-      <c r="I6" s="41">
-        <v>0.472222222222222</v>
+      <c r="I6" s="36">
+        <v>0.47222222222222199</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46">
+      <c r="K6" s="41"/>
+      <c r="L6" s="41"/>
+      <c r="M6" s="41">
         <v>15917557</v>
       </c>
-      <c r="N6" s="46">
+      <c r="N6" s="41">
         <v>5</v>
       </c>
     </row>
-    <row r="7" ht="19.9" customHeight="1" spans="1:14">
+    <row r="7" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A7" s="14">
         <v>2</v>
       </c>
@@ -2419,32 +1801,32 @@
       <c r="F7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G7" s="40">
+      <c r="G7" s="35">
         <v>46292</v>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="36">
         <v>0.211805555555556</v>
       </c>
-      <c r="I7" s="41">
-        <v>0.472222222222222</v>
+      <c r="I7" s="36">
+        <v>0.47222222222222199</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="K7" s="46">
+      <c r="K7" s="41">
         <v>6</v>
       </c>
-      <c r="L7" s="46">
+      <c r="L7" s="41">
         <v>1320</v>
       </c>
-      <c r="M7" s="46">
+      <c r="M7" s="41">
         <v>15917557</v>
       </c>
-      <c r="N7" s="46">
+      <c r="N7" s="41">
         <v>5</v>
       </c>
     </row>
-    <row r="8" ht="19.9" customHeight="1" spans="1:14">
+    <row r="8" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A8" s="14">
         <v>3</v>
       </c>
@@ -2463,28 +1845,28 @@
       <c r="F8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G8" s="35">
         <v>46292</v>
       </c>
-      <c r="H8" s="41">
+      <c r="H8" s="36">
         <v>0.211805555555556</v>
       </c>
-      <c r="I8" s="41">
-        <v>0.472222222222222</v>
+      <c r="I8" s="36">
+        <v>0.47222222222222199</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="K8" s="46"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="46">
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
+      <c r="M8" s="41">
         <v>15917557</v>
       </c>
-      <c r="N8" s="46">
+      <c r="N8" s="41">
         <v>5</v>
       </c>
     </row>
-    <row r="9" ht="19.9" customHeight="1" spans="1:14">
+    <row r="9" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A9" s="14">
         <v>4</v>
       </c>
@@ -2503,28 +1885,28 @@
       <c r="F9" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="40">
+      <c r="G9" s="35">
         <v>46292</v>
       </c>
-      <c r="H9" s="41">
+      <c r="H9" s="36">
         <v>0.211805555555556</v>
       </c>
-      <c r="I9" s="41">
-        <v>0.472222222222222</v>
+      <c r="I9" s="36">
+        <v>0.47222222222222199</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="K9" s="46"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46">
+      <c r="K9" s="41"/>
+      <c r="L9" s="41"/>
+      <c r="M9" s="41">
         <v>15917557</v>
       </c>
-      <c r="N9" s="46">
+      <c r="N9" s="41">
         <v>5</v>
       </c>
     </row>
-    <row r="10" ht="19.9" customHeight="1" spans="1:14">
+    <row r="10" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A10" s="14">
         <v>5</v>
       </c>
@@ -2543,28 +1925,28 @@
       <c r="F10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="40">
+      <c r="G10" s="35">
         <v>46292</v>
       </c>
-      <c r="H10" s="41">
+      <c r="H10" s="36">
         <v>0.211805555555556</v>
       </c>
-      <c r="I10" s="41">
-        <v>0.472222222222222</v>
+      <c r="I10" s="36">
+        <v>0.47222222222222199</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="46"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46">
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41">
         <v>15917557</v>
       </c>
-      <c r="N10" s="46">
+      <c r="N10" s="41">
         <v>5</v>
       </c>
     </row>
-    <row r="11" ht="19.9" customHeight="1" spans="1:14">
+    <row r="11" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A11" s="14">
         <v>6</v>
       </c>
@@ -2583,28 +1965,28 @@
       <c r="F11" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="40">
+      <c r="G11" s="35">
         <v>46292</v>
       </c>
-      <c r="H11" s="41">
+      <c r="H11" s="36">
         <v>0.211805555555556</v>
       </c>
-      <c r="I11" s="41">
-        <v>0.472222222222222</v>
+      <c r="I11" s="36">
+        <v>0.47222222222222199</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="K11" s="46"/>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46">
+      <c r="K11" s="41"/>
+      <c r="L11" s="41"/>
+      <c r="M11" s="41">
         <v>15917557</v>
       </c>
-      <c r="N11" s="46">
+      <c r="N11" s="41">
         <v>5</v>
       </c>
     </row>
-    <row r="12" ht="19.9" customHeight="1" spans="1:14">
+    <row r="12" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A12" s="14">
         <v>7</v>
       </c>
@@ -2623,32 +2005,32 @@
       <c r="F12" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="47">
+      <c r="G12" s="42">
         <v>46292</v>
       </c>
       <c r="H12" s="10">
         <v>5.05</v>
       </c>
-      <c r="I12" s="48">
+      <c r="I12" s="43">
         <v>11.2</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="K12" s="46">
+      <c r="K12" s="41">
         <v>6</v>
       </c>
-      <c r="L12" s="46">
+      <c r="L12" s="41">
         <v>1320</v>
       </c>
-      <c r="M12" s="46">
+      <c r="M12" s="41">
         <v>15917553</v>
       </c>
-      <c r="N12" s="46">
+      <c r="N12" s="41">
         <v>3</v>
       </c>
     </row>
-    <row r="13" ht="19.9" customHeight="1" spans="1:14">
+    <row r="13" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A13" s="14">
         <v>8</v>
       </c>
@@ -2667,28 +2049,28 @@
       <c r="F13" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G13" s="47">
+      <c r="G13" s="42">
         <v>46292</v>
       </c>
       <c r="H13" s="10">
         <v>5.05</v>
       </c>
-      <c r="I13" s="48">
+      <c r="I13" s="43">
         <v>11.2</v>
       </c>
       <c r="J13" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="K13" s="46"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46">
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41">
         <v>15917553</v>
       </c>
-      <c r="N13" s="46">
+      <c r="N13" s="41">
         <v>3</v>
       </c>
     </row>
-    <row r="14" ht="19.9" customHeight="1" spans="1:14">
+    <row r="14" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A14" s="14">
         <v>9</v>
       </c>
@@ -2707,28 +2089,28 @@
       <c r="F14" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G14" s="47">
+      <c r="G14" s="42">
         <v>46292</v>
       </c>
       <c r="H14" s="10">
         <v>5.05</v>
       </c>
-      <c r="I14" s="48">
+      <c r="I14" s="43">
         <v>11.2</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="K14" s="46"/>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46">
+      <c r="K14" s="41"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="41">
         <v>15917553</v>
       </c>
-      <c r="N14" s="46">
+      <c r="N14" s="41">
         <v>3</v>
       </c>
     </row>
-    <row r="15" ht="19.9" customHeight="1" spans="1:14">
+    <row r="15" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A15" s="14">
         <v>10</v>
       </c>
@@ -2747,28 +2129,28 @@
       <c r="F15" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="47">
+      <c r="G15" s="42">
         <v>46292</v>
       </c>
       <c r="H15" s="10">
         <v>5.05</v>
       </c>
-      <c r="I15" s="48">
+      <c r="I15" s="43">
         <v>11.2</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46">
+      <c r="K15" s="41"/>
+      <c r="L15" s="41"/>
+      <c r="M15" s="41">
         <v>15917553</v>
       </c>
-      <c r="N15" s="46">
+      <c r="N15" s="41">
         <v>3</v>
       </c>
     </row>
-    <row r="16" ht="19.9" customHeight="1" spans="1:14">
+    <row r="16" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A16" s="14">
         <v>11</v>
       </c>
@@ -2787,28 +2169,28 @@
       <c r="F16" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G16" s="47">
+      <c r="G16" s="42">
         <v>46292</v>
       </c>
       <c r="H16" s="10">
         <v>5.05</v>
       </c>
-      <c r="I16" s="48">
+      <c r="I16" s="43">
         <v>11.2</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="K16" s="46"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46">
+      <c r="K16" s="41"/>
+      <c r="L16" s="41"/>
+      <c r="M16" s="41">
         <v>15917553</v>
       </c>
-      <c r="N16" s="46">
+      <c r="N16" s="41">
         <v>3</v>
       </c>
     </row>
-    <row r="17" ht="19.9" customHeight="1" spans="1:14">
+    <row r="17" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A17" s="14">
         <v>12</v>
       </c>
@@ -2827,28 +2209,28 @@
       <c r="F17" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="G17" s="47">
+      <c r="G17" s="42">
         <v>46292</v>
       </c>
       <c r="H17" s="10">
         <v>5.05</v>
       </c>
-      <c r="I17" s="48">
+      <c r="I17" s="43">
         <v>11.2</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="K17" s="46"/>
-      <c r="L17" s="46"/>
-      <c r="M17" s="46">
+      <c r="K17" s="41"/>
+      <c r="L17" s="41"/>
+      <c r="M17" s="41">
         <v>15917553</v>
       </c>
-      <c r="N17" s="46">
+      <c r="N17" s="41">
         <v>3</v>
       </c>
     </row>
-    <row r="18" ht="19.9" customHeight="1" spans="1:14">
+    <row r="18" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A18" s="14">
         <v>13</v>
       </c>
@@ -2867,28 +2249,28 @@
       <c r="F18" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G18" s="40">
+      <c r="G18" s="35">
         <v>46292</v>
       </c>
       <c r="H18" s="10">
         <v>5.05</v>
       </c>
-      <c r="I18" s="24">
+      <c r="I18" s="19">
         <v>11.2</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="K18" s="46"/>
-      <c r="L18" s="46"/>
-      <c r="M18" s="46">
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41">
         <v>15917555</v>
       </c>
-      <c r="N18" s="46">
+      <c r="N18" s="41">
         <v>4</v>
       </c>
     </row>
-    <row r="19" ht="19.9" customHeight="1" spans="1:14">
+    <row r="19" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A19" s="14">
         <v>14</v>
       </c>
@@ -2907,28 +2289,28 @@
       <c r="F19" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G19" s="40">
+      <c r="G19" s="35">
         <v>46292</v>
       </c>
       <c r="H19" s="10">
         <v>5.05</v>
       </c>
-      <c r="I19" s="24">
+      <c r="I19" s="19">
         <v>11.2</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46">
+      <c r="K19" s="41"/>
+      <c r="L19" s="41"/>
+      <c r="M19" s="41">
         <v>15917555</v>
       </c>
-      <c r="N19" s="46">
+      <c r="N19" s="41">
         <v>4</v>
       </c>
     </row>
-    <row r="20" ht="19.9" customHeight="1" spans="1:14">
+    <row r="20" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A20" s="14">
         <v>15</v>
       </c>
@@ -2947,32 +2329,32 @@
       <c r="F20" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G20" s="40">
+      <c r="G20" s="35">
         <v>46292</v>
       </c>
       <c r="H20" s="10">
         <v>5.05</v>
       </c>
-      <c r="I20" s="24">
+      <c r="I20" s="19">
         <v>11.2</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="K20" s="46">
+      <c r="K20" s="41">
         <v>6</v>
       </c>
-      <c r="L20" s="46">
+      <c r="L20" s="41">
         <v>1320</v>
       </c>
-      <c r="M20" s="46">
+      <c r="M20" s="41">
         <v>15917555</v>
       </c>
-      <c r="N20" s="46">
+      <c r="N20" s="41">
         <v>4</v>
       </c>
     </row>
-    <row r="21" ht="19.9" customHeight="1" spans="1:14">
+    <row r="21" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A21" s="14">
         <v>16</v>
       </c>
@@ -2991,28 +2373,28 @@
       <c r="F21" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G21" s="40">
+      <c r="G21" s="35">
         <v>46292</v>
       </c>
       <c r="H21" s="10">
         <v>5.05</v>
       </c>
-      <c r="I21" s="24">
+      <c r="I21" s="19">
         <v>11.2</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="K21" s="46"/>
-      <c r="L21" s="46"/>
-      <c r="M21" s="46">
+      <c r="K21" s="41"/>
+      <c r="L21" s="41"/>
+      <c r="M21" s="41">
         <v>15917555</v>
       </c>
-      <c r="N21" s="46">
+      <c r="N21" s="41">
         <v>4</v>
       </c>
     </row>
-    <row r="22" ht="19.9" customHeight="1" spans="1:14">
+    <row r="22" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A22" s="14">
         <v>17</v>
       </c>
@@ -3031,28 +2413,28 @@
       <c r="F22" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="40">
+      <c r="G22" s="35">
         <v>46292</v>
       </c>
       <c r="H22" s="10">
         <v>5.05</v>
       </c>
-      <c r="I22" s="24">
+      <c r="I22" s="19">
         <v>11.2</v>
       </c>
       <c r="J22" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="K22" s="46"/>
-      <c r="L22" s="46"/>
-      <c r="M22" s="46">
+      <c r="K22" s="41"/>
+      <c r="L22" s="41"/>
+      <c r="M22" s="41">
         <v>15917555</v>
       </c>
-      <c r="N22" s="46">
+      <c r="N22" s="41">
         <v>4</v>
       </c>
     </row>
-    <row r="23" ht="19.9" customHeight="1" spans="1:14">
+    <row r="23" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A23" s="14">
         <v>18</v>
       </c>
@@ -3071,42 +2453,42 @@
       <c r="F23" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G23" s="40">
+      <c r="G23" s="35">
         <v>46292</v>
       </c>
       <c r="H23" s="10">
         <v>5.05</v>
       </c>
-      <c r="I23" s="24">
+      <c r="I23" s="19">
         <v>11.2</v>
       </c>
       <c r="J23" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="K23" s="46"/>
-      <c r="L23" s="46"/>
-      <c r="M23" s="46">
+      <c r="K23" s="41"/>
+      <c r="L23" s="41"/>
+      <c r="M23" s="41">
         <v>15917555</v>
       </c>
-      <c r="N23" s="46">
+      <c r="N23" s="41">
         <v>4</v>
       </c>
     </row>
     <row r="24" spans="1:14">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
-      <c r="K24" s="17"/>
-      <c r="L24" s="17"/>
-      <c r="M24" s="17"/>
-      <c r="N24" s="17"/>
+      <c r="A24" s="45"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="F24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3114,8 +2496,7 @@
     <mergeCell ref="A24:N24"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" scale="80" orientation="landscape"/>
-  <headerFooter/>
+  <pageSetup scale="80" orientation="landscape" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="12" max="1048575" man="1"/>
   </colBreaks>
@@ -3123,19 +2504,18 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A2:N22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="7" max="7" width="11.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="9.71428571428571" customWidth="1"/>
-    <col min="10" max="10" width="16.4285714285714" customWidth="1"/>
-    <col min="14" max="14" width="9.71428571428571" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="26.25" spans="1:14">
+    <row r="2" spans="1:14" ht="26.25">
       <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3143,7 +2523,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" ht="26.25" spans="1:14">
+    <row r="3" spans="1:14" ht="26.25">
       <c r="A3" s="5"/>
       <c r="B3" s="4" t="s">
         <v>1</v>
@@ -3155,10 +2535,10 @@
       <c r="E3" s="7"/>
       <c r="F3" s="8"/>
       <c r="G3" s="6"/>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="16" t="s">
         <v>3</v>
       </c>
       <c r="J3" s="5"/>
@@ -3210,10 +2590,10 @@
       <c r="N4" s="5"/>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="42">
+      <c r="A5" s="37">
         <v>1</v>
       </c>
-      <c r="B5" s="43">
+      <c r="B5" s="38">
         <v>19031</v>
       </c>
       <c r="C5" s="13" t="s">
@@ -3228,36 +2608,36 @@
       <c r="F5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="44">
-        <v>46291</v>
-      </c>
-      <c r="H5" s="42">
+      <c r="G5" s="39">
+        <v>46291</v>
+      </c>
+      <c r="H5" s="37">
         <v>11.25</v>
       </c>
-      <c r="I5" s="45">
+      <c r="I5" s="40">
         <v>4.5</v>
       </c>
-      <c r="J5" s="46" t="s">
+      <c r="J5" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="K5" s="42">
+      <c r="K5" s="37">
         <v>6</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="37">
         <v>3150</v>
       </c>
-      <c r="M5" s="42">
+      <c r="M5" s="37">
         <v>15917554</v>
       </c>
-      <c r="N5" s="42">
+      <c r="N5" s="37">
         <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="42">
+      <c r="A6" s="37">
         <v>2</v>
       </c>
-      <c r="B6" s="43">
+      <c r="B6" s="38">
         <v>19031</v>
       </c>
       <c r="C6" s="13" t="s">
@@ -3272,32 +2652,32 @@
       <c r="F6" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="44">
-        <v>46291</v>
-      </c>
-      <c r="H6" s="42">
+      <c r="G6" s="39">
+        <v>46291</v>
+      </c>
+      <c r="H6" s="37">
         <v>11.25</v>
       </c>
-      <c r="I6" s="45">
+      <c r="I6" s="40">
         <v>4.5</v>
       </c>
-      <c r="J6" s="46" t="s">
+      <c r="J6" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42">
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
+      <c r="M6" s="37">
         <v>15917554</v>
       </c>
-      <c r="N6" s="42">
+      <c r="N6" s="37">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="42">
+      <c r="A7" s="37">
         <v>3</v>
       </c>
-      <c r="B7" s="43">
+      <c r="B7" s="38">
         <v>19031</v>
       </c>
       <c r="C7" s="13" t="s">
@@ -3312,32 +2692,32 @@
       <c r="F7" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="44">
-        <v>46291</v>
-      </c>
-      <c r="H7" s="42">
+      <c r="G7" s="39">
+        <v>46291</v>
+      </c>
+      <c r="H7" s="37">
         <v>11.25</v>
       </c>
-      <c r="I7" s="45">
+      <c r="I7" s="40">
         <v>4.5</v>
       </c>
-      <c r="J7" s="46" t="s">
+      <c r="J7" s="41" t="s">
         <v>59</v>
       </c>
-      <c r="K7" s="42"/>
-      <c r="L7" s="42"/>
-      <c r="M7" s="42">
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+      <c r="M7" s="37">
         <v>15917554</v>
       </c>
-      <c r="N7" s="42">
+      <c r="N7" s="37">
         <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="42">
+      <c r="A8" s="37">
         <v>4</v>
       </c>
-      <c r="B8" s="43">
+      <c r="B8" s="38">
         <v>19031</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -3352,32 +2732,32 @@
       <c r="F8" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="44">
-        <v>46291</v>
-      </c>
-      <c r="H8" s="42">
+      <c r="G8" s="39">
+        <v>46291</v>
+      </c>
+      <c r="H8" s="37">
         <v>11.25</v>
       </c>
-      <c r="I8" s="45">
+      <c r="I8" s="40">
         <v>4.5</v>
       </c>
-      <c r="J8" s="46" t="s">
+      <c r="J8" s="41" t="s">
         <v>60</v>
       </c>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42">
+      <c r="K8" s="37"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="37">
         <v>15917554</v>
       </c>
-      <c r="N8" s="42">
+      <c r="N8" s="37">
         <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="42">
+      <c r="A9" s="37">
         <v>5</v>
       </c>
-      <c r="B9" s="43">
+      <c r="B9" s="38">
         <v>19031</v>
       </c>
       <c r="C9" s="13" t="s">
@@ -3392,32 +2772,32 @@
       <c r="F9" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G9" s="44">
-        <v>46291</v>
-      </c>
-      <c r="H9" s="42">
+      <c r="G9" s="39">
+        <v>46291</v>
+      </c>
+      <c r="H9" s="37">
         <v>11.25</v>
       </c>
-      <c r="I9" s="45">
+      <c r="I9" s="40">
         <v>4.5</v>
       </c>
-      <c r="J9" s="46" t="s">
+      <c r="J9" s="41" t="s">
         <v>61</v>
       </c>
-      <c r="K9" s="42"/>
-      <c r="L9" s="42"/>
-      <c r="M9" s="42">
+      <c r="K9" s="37"/>
+      <c r="L9" s="37"/>
+      <c r="M9" s="37">
         <v>15917554</v>
       </c>
-      <c r="N9" s="42">
+      <c r="N9" s="37">
         <v>4</v>
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="42">
+      <c r="A10" s="37">
         <v>6</v>
       </c>
-      <c r="B10" s="43">
+      <c r="B10" s="38">
         <v>19031</v>
       </c>
       <c r="C10" s="13" t="s">
@@ -3432,32 +2812,32 @@
       <c r="F10" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="44">
-        <v>46291</v>
-      </c>
-      <c r="H10" s="42">
+      <c r="G10" s="39">
+        <v>46291</v>
+      </c>
+      <c r="H10" s="37">
         <v>11.25</v>
       </c>
-      <c r="I10" s="45">
+      <c r="I10" s="40">
         <v>4.5</v>
       </c>
-      <c r="J10" s="46" t="s">
+      <c r="J10" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42">
+      <c r="K10" s="37"/>
+      <c r="L10" s="37"/>
+      <c r="M10" s="37">
         <v>15917554</v>
       </c>
-      <c r="N10" s="42">
+      <c r="N10" s="37">
         <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="42">
+      <c r="A11" s="37">
         <v>7</v>
       </c>
-      <c r="B11" s="43">
+      <c r="B11" s="38">
         <v>19031</v>
       </c>
       <c r="C11" s="13" t="s">
@@ -3476,12 +2856,12 @@
         <v>46291</v>
       </c>
       <c r="H11" s="9">
-        <v>0.475694444444444</v>
+        <v>0.47569444444444398</v>
       </c>
       <c r="I11" s="9">
-        <v>0.201388888888889</v>
-      </c>
-      <c r="J11" s="46" t="s">
+        <v>0.20138888888888901</v>
+      </c>
+      <c r="J11" s="41" t="s">
         <v>63</v>
       </c>
       <c r="K11" s="5"/>
@@ -3494,10 +2874,10 @@
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="42">
+      <c r="A12" s="37">
         <v>8</v>
       </c>
-      <c r="B12" s="43">
+      <c r="B12" s="38">
         <v>19031</v>
       </c>
       <c r="C12" s="13" t="s">
@@ -3518,10 +2898,10 @@
       <c r="H12" s="5">
         <v>11.25</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="17">
         <v>4.5</v>
       </c>
-      <c r="J12" s="46" t="s">
+      <c r="J12" s="41" t="s">
         <v>33</v>
       </c>
       <c r="K12" s="5">
@@ -3538,10 +2918,10 @@
       </c>
     </row>
     <row r="13" spans="1:14">
-      <c r="A13" s="42">
+      <c r="A13" s="37">
         <v>9</v>
       </c>
-      <c r="B13" s="43">
+      <c r="B13" s="38">
         <v>19031</v>
       </c>
       <c r="C13" s="13" t="s">
@@ -3562,10 +2942,10 @@
       <c r="H13" s="5">
         <v>11.25</v>
       </c>
-      <c r="I13" s="20">
+      <c r="I13" s="17">
         <v>4.5</v>
       </c>
-      <c r="J13" s="46" t="s">
+      <c r="J13" s="41" t="s">
         <v>35</v>
       </c>
       <c r="K13" s="5"/>
@@ -3578,10 +2958,10 @@
       </c>
     </row>
     <row r="14" spans="1:14">
-      <c r="A14" s="42">
-        <v>10</v>
-      </c>
-      <c r="B14" s="43">
+      <c r="A14" s="37">
+        <v>10</v>
+      </c>
+      <c r="B14" s="38">
         <v>19031</v>
       </c>
       <c r="C14" s="13" t="s">
@@ -3602,10 +2982,10 @@
       <c r="H14" s="5">
         <v>11.25</v>
       </c>
-      <c r="I14" s="20">
+      <c r="I14" s="17">
         <v>4.5</v>
       </c>
-      <c r="J14" s="46" t="s">
+      <c r="J14" s="41" t="s">
         <v>37</v>
       </c>
       <c r="K14" s="5"/>
@@ -3618,10 +2998,10 @@
       </c>
     </row>
     <row r="15" spans="1:14">
-      <c r="A15" s="42">
+      <c r="A15" s="37">
         <v>11</v>
       </c>
-      <c r="B15" s="43">
+      <c r="B15" s="38">
         <v>19031</v>
       </c>
       <c r="C15" s="13" t="s">
@@ -3642,10 +3022,10 @@
       <c r="H15" s="5">
         <v>11.25</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="17">
         <v>4.5</v>
       </c>
-      <c r="J15" s="46" t="s">
+      <c r="J15" s="41" t="s">
         <v>39</v>
       </c>
       <c r="K15" s="5"/>
@@ -3658,10 +3038,10 @@
       </c>
     </row>
     <row r="16" spans="1:14">
-      <c r="A16" s="42">
+      <c r="A16" s="37">
         <v>12</v>
       </c>
-      <c r="B16" s="43">
+      <c r="B16" s="38">
         <v>19031</v>
       </c>
       <c r="C16" s="13" t="s">
@@ -3682,10 +3062,10 @@
       <c r="H16" s="5">
         <v>11.25</v>
       </c>
-      <c r="I16" s="20">
+      <c r="I16" s="17">
         <v>4.5</v>
       </c>
-      <c r="J16" s="46" t="s">
+      <c r="J16" s="41" t="s">
         <v>41</v>
       </c>
       <c r="K16" s="5"/>
@@ -3698,10 +3078,10 @@
       </c>
     </row>
     <row r="17" spans="1:14">
-      <c r="A17" s="42">
+      <c r="A17" s="37">
         <v>13</v>
       </c>
-      <c r="B17" s="43">
+      <c r="B17" s="38">
         <v>19031</v>
       </c>
       <c r="C17" s="13" t="s">
@@ -3722,10 +3102,10 @@
       <c r="H17" s="5">
         <v>11.25</v>
       </c>
-      <c r="I17" s="20">
+      <c r="I17" s="17">
         <v>4.5</v>
       </c>
-      <c r="J17" s="46" t="s">
+      <c r="J17" s="41" t="s">
         <v>43</v>
       </c>
       <c r="K17" s="5"/>
@@ -3738,10 +3118,10 @@
       </c>
     </row>
     <row r="18" spans="1:14">
-      <c r="A18" s="42">
+      <c r="A18" s="37">
         <v>14</v>
       </c>
-      <c r="B18" s="43">
+      <c r="B18" s="38">
         <v>19031</v>
       </c>
       <c r="C18" s="13" t="s">
@@ -3760,12 +3140,12 @@
         <v>46291</v>
       </c>
       <c r="H18" s="9">
-        <v>0.475694444444444</v>
+        <v>0.47569444444444398</v>
       </c>
       <c r="I18" s="9">
-        <v>0.201388888888889</v>
-      </c>
-      <c r="J18" s="46" t="s">
+        <v>0.20138888888888901</v>
+      </c>
+      <c r="J18" s="41" t="s">
         <v>64</v>
       </c>
       <c r="K18" s="5"/>
@@ -3778,10 +3158,10 @@
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="42">
+      <c r="A19" s="37">
         <v>15</v>
       </c>
-      <c r="B19" s="43">
+      <c r="B19" s="38">
         <v>19031</v>
       </c>
       <c r="C19" s="13" t="s">
@@ -3800,12 +3180,12 @@
         <v>46291</v>
       </c>
       <c r="H19" s="9">
-        <v>0.475694444444444</v>
+        <v>0.47569444444444398</v>
       </c>
       <c r="I19" s="9">
-        <v>0.201388888888889</v>
-      </c>
-      <c r="J19" s="46" t="s">
+        <v>0.20138888888888901</v>
+      </c>
+      <c r="J19" s="41" t="s">
         <v>65</v>
       </c>
       <c r="K19" s="5">
@@ -3822,10 +3202,10 @@
       </c>
     </row>
     <row r="20" spans="1:14">
-      <c r="A20" s="42">
+      <c r="A20" s="37">
         <v>16</v>
       </c>
-      <c r="B20" s="43">
+      <c r="B20" s="38">
         <v>19031</v>
       </c>
       <c r="C20" s="13" t="s">
@@ -3844,12 +3224,12 @@
         <v>46291</v>
       </c>
       <c r="H20" s="9">
-        <v>0.475694444444444</v>
+        <v>0.47569444444444398</v>
       </c>
       <c r="I20" s="9">
-        <v>0.201388888888889</v>
-      </c>
-      <c r="J20" s="46" t="s">
+        <v>0.20138888888888901</v>
+      </c>
+      <c r="J20" s="41" t="s">
         <v>66</v>
       </c>
       <c r="K20" s="5"/>
@@ -3862,10 +3242,10 @@
       </c>
     </row>
     <row r="21" spans="1:14">
-      <c r="A21" s="42">
+      <c r="A21" s="37">
         <v>17</v>
       </c>
-      <c r="B21" s="43">
+      <c r="B21" s="38">
         <v>19031</v>
       </c>
       <c r="C21" s="13" t="s">
@@ -3884,12 +3264,12 @@
         <v>46291</v>
       </c>
       <c r="H21" s="9">
-        <v>0.475694444444444</v>
+        <v>0.47569444444444398</v>
       </c>
       <c r="I21" s="9">
-        <v>0.201388888888889</v>
-      </c>
-      <c r="J21" s="46" t="s">
+        <v>0.20138888888888901</v>
+      </c>
+      <c r="J21" s="41" t="s">
         <v>67</v>
       </c>
       <c r="K21" s="5"/>
@@ -3902,10 +3282,10 @@
       </c>
     </row>
     <row r="22" spans="1:14">
-      <c r="A22" s="42">
+      <c r="A22" s="37">
         <v>18</v>
       </c>
-      <c r="B22" s="43">
+      <c r="B22" s="38">
         <v>19031</v>
       </c>
       <c r="C22" s="13" t="s">
@@ -3924,12 +3304,12 @@
         <v>46291</v>
       </c>
       <c r="H22" s="9">
-        <v>0.475694444444444</v>
+        <v>0.47569444444444398</v>
       </c>
       <c r="I22" s="9">
-        <v>0.201388888888889</v>
-      </c>
-      <c r="J22" s="46" t="s">
+        <v>0.20138888888888901</v>
+      </c>
+      <c r="J22" s="41" t="s">
         <v>68</v>
       </c>
       <c r="K22" s="5"/>
@@ -3943,30 +3323,28 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="landscape"/>
-  <headerFooter/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A2:O78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="32.4285714285714" customWidth="1"/>
+    <col min="3" max="3" width="32.42578125" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
-    <col min="7" max="7" width="11.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="7.57142857142857" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="8" max="8" width="7.5703125" customWidth="1"/>
     <col min="9" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="16.7142857142857" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" customWidth="1"/>
     <col min="11" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="10.1428571428571" customWidth="1"/>
-    <col min="14" max="14" width="9.71428571428571" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="26.25" spans="1:14">
+    <row r="2" spans="1:14" ht="26.25">
       <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3975,20 +3353,20 @@
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="16"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="18"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="46"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="4" t="s">
@@ -4053,10 +3431,10 @@
         <v>46291</v>
       </c>
       <c r="H5" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I5" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>71</v>
@@ -4095,10 +3473,10 @@
         <v>46291</v>
       </c>
       <c r="H6" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I6" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>73</v>
@@ -4135,10 +3513,10 @@
         <v>46291</v>
       </c>
       <c r="H7" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I7" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>75</v>
@@ -4175,10 +3553,10 @@
         <v>46291</v>
       </c>
       <c r="H8" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I8" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>77</v>
@@ -4213,10 +3591,10 @@
         <v>46291</v>
       </c>
       <c r="H9" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I9" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>79</v>
@@ -4251,10 +3629,10 @@
         <v>46291</v>
       </c>
       <c r="H10" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I10" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>81</v>
@@ -4289,10 +3667,10 @@
         <v>46291</v>
       </c>
       <c r="H11" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I11" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>83</v>
@@ -4327,10 +3705,10 @@
         <v>46291</v>
       </c>
       <c r="H12" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I12" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>85</v>
@@ -4369,10 +3747,10 @@
         <v>46291</v>
       </c>
       <c r="H13" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I13" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>87</v>
@@ -4407,10 +3785,10 @@
         <v>46291</v>
       </c>
       <c r="H14" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I14" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>89</v>
@@ -4447,10 +3825,10 @@
         <v>46291</v>
       </c>
       <c r="H15" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I15" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>91</v>
@@ -4487,10 +3865,10 @@
         <v>46291</v>
       </c>
       <c r="H16" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I16" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>93</v>
@@ -4525,10 +3903,10 @@
         <v>46291</v>
       </c>
       <c r="H17" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I17" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>95</v>
@@ -4563,10 +3941,10 @@
         <v>46291</v>
       </c>
       <c r="H18" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I18" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>97</v>
@@ -4605,10 +3983,10 @@
         <v>46291</v>
       </c>
       <c r="H19" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I19" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>99</v>
@@ -4643,10 +4021,10 @@
         <v>46291</v>
       </c>
       <c r="H20" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I20" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>101</v>
@@ -4685,10 +4063,10 @@
         <v>46291</v>
       </c>
       <c r="H21" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I21" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>103</v>
@@ -4723,10 +4101,10 @@
         <v>46291</v>
       </c>
       <c r="H22" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I22" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>105</v>
@@ -4761,10 +4139,10 @@
         <v>46291</v>
       </c>
       <c r="H23" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I23" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>107</v>
@@ -4803,10 +4181,10 @@
         <v>46291</v>
       </c>
       <c r="H24" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I24" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>109</v>
@@ -4841,10 +4219,10 @@
         <v>46291</v>
       </c>
       <c r="H25" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I25" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>111</v>
@@ -4879,10 +4257,10 @@
         <v>46291</v>
       </c>
       <c r="H26" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I26" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>113</v>
@@ -4917,10 +4295,10 @@
         <v>46291</v>
       </c>
       <c r="H27" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I27" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>115</v>
@@ -4958,10 +4336,10 @@
         <v>46291</v>
       </c>
       <c r="H28" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I28" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>118</v>
@@ -5000,10 +4378,10 @@
         <v>46291</v>
       </c>
       <c r="H29" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I29" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>120</v>
@@ -5038,10 +4416,10 @@
         <v>46291</v>
       </c>
       <c r="H30" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I30" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>122</v>
@@ -5080,10 +4458,10 @@
         <v>46291</v>
       </c>
       <c r="H31" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I31" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>124</v>
@@ -5118,10 +4496,10 @@
         <v>46291</v>
       </c>
       <c r="H32" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I32" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>126</v>
@@ -5158,7 +4536,7 @@
         <v>46291</v>
       </c>
       <c r="H33" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I33" s="12" t="s">
         <v>128</v>
@@ -5202,7 +4580,7 @@
         <v>46291</v>
       </c>
       <c r="H34" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I34" s="12" t="s">
         <v>128</v>
@@ -5242,7 +4620,7 @@
         <v>46291</v>
       </c>
       <c r="H35" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I35" s="12" t="s">
         <v>128</v>
@@ -5282,7 +4660,7 @@
         <v>46291</v>
       </c>
       <c r="H36" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I36" s="12" t="s">
         <v>128</v>
@@ -5322,10 +4700,10 @@
         <v>46291</v>
       </c>
       <c r="H37" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I37" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J37" s="5" t="s">
         <v>137</v>
@@ -5362,10 +4740,10 @@
         <v>46291</v>
       </c>
       <c r="H38" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I38" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J38" s="5" t="s">
         <v>139</v>
@@ -5406,10 +4784,10 @@
         <v>46291</v>
       </c>
       <c r="H39" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I39" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J39" s="5" t="s">
         <v>141</v>
@@ -5448,10 +4826,10 @@
         <v>46291</v>
       </c>
       <c r="H40" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I40" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J40" s="5" t="s">
         <v>143</v>
@@ -5490,10 +4868,10 @@
         <v>46291</v>
       </c>
       <c r="H41" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I41" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J41" s="5" t="s">
         <v>145</v>
@@ -5532,10 +4910,10 @@
         <v>46291</v>
       </c>
       <c r="H42" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I42" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J42" s="5" t="s">
         <v>147</v>
@@ -5574,10 +4952,10 @@
         <v>46291</v>
       </c>
       <c r="H43" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I43" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J43" s="5" t="s">
         <v>149</v>
@@ -5618,10 +4996,10 @@
         <v>46291</v>
       </c>
       <c r="H44" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I44" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J44" s="5" t="s">
         <v>151</v>
@@ -5658,10 +5036,10 @@
         <v>46291</v>
       </c>
       <c r="H45" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I45" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J45" s="5" t="s">
         <v>153</v>
@@ -5702,10 +5080,10 @@
         <v>46291</v>
       </c>
       <c r="H46" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I46" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J46" s="5" t="s">
         <v>22</v>
@@ -5740,10 +5118,10 @@
         <v>46291</v>
       </c>
       <c r="H47" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I47" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J47" s="5" t="s">
         <v>25</v>
@@ -5784,10 +5162,10 @@
         <v>46291</v>
       </c>
       <c r="H48" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I48" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J48" s="5" t="s">
         <v>157</v>
@@ -5828,10 +5206,10 @@
         <v>46291</v>
       </c>
       <c r="H49" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I49" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J49" s="5" t="s">
         <v>159</v>
@@ -5868,10 +5246,10 @@
         <v>46291</v>
       </c>
       <c r="H50" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I50" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J50" s="5" t="s">
         <v>161</v>
@@ -5906,10 +5284,10 @@
         <v>46291</v>
       </c>
       <c r="H51" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I51" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>163</v>
@@ -5950,10 +5328,10 @@
         <v>46291</v>
       </c>
       <c r="H52" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I52" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J52" s="5" t="s">
         <v>165</v>
@@ -5988,10 +5366,10 @@
         <v>46291</v>
       </c>
       <c r="H53" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I53" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J53" s="5" t="s">
         <v>167</v>
@@ -6030,10 +5408,10 @@
         <v>46291</v>
       </c>
       <c r="H54" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I54" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J54" s="5" t="s">
         <v>169</v>
@@ -6070,10 +5448,10 @@
         <v>46291</v>
       </c>
       <c r="H55" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I55" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J55" s="5" t="s">
         <v>171</v>
@@ -6108,10 +5486,10 @@
         <v>46291</v>
       </c>
       <c r="H56" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I56" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J56" s="5" t="s">
         <v>173</v>
@@ -6144,10 +5522,10 @@
         <v>46291</v>
       </c>
       <c r="H57" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I57" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J57" s="5" t="s">
         <v>175</v>
@@ -6184,10 +5562,10 @@
         <v>46291</v>
       </c>
       <c r="H58" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I58" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J58" s="5" t="s">
         <v>177</v>
@@ -6226,10 +5604,10 @@
         <v>46291</v>
       </c>
       <c r="H59" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I59" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>179</v>
@@ -6266,10 +5644,10 @@
         <v>46291</v>
       </c>
       <c r="H60" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I60" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J60" s="5" t="s">
         <v>181</v>
@@ -6308,10 +5686,10 @@
         <v>46291</v>
       </c>
       <c r="H61" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I61" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J61" s="5" t="s">
         <v>183</v>
@@ -6346,10 +5724,10 @@
         <v>46291</v>
       </c>
       <c r="H62" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I62" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J62" s="5" t="s">
         <v>185</v>
@@ -6386,10 +5764,10 @@
         <v>46291</v>
       </c>
       <c r="H63" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I63" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J63" s="5" t="s">
         <v>187</v>
@@ -6426,10 +5804,10 @@
         <v>46291</v>
       </c>
       <c r="H64" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I64" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J64" s="5" t="s">
         <v>189</v>
@@ -6470,10 +5848,10 @@
         <v>46291</v>
       </c>
       <c r="H65" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I65" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>191</v>
@@ -6514,10 +5892,10 @@
         <v>46291</v>
       </c>
       <c r="H66" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I66" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>193</v>
@@ -6552,10 +5930,10 @@
         <v>46291</v>
       </c>
       <c r="H67" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I67" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>57</v>
@@ -6594,10 +5972,10 @@
         <v>46291</v>
       </c>
       <c r="H68" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I68" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>60</v>
@@ -6634,10 +6012,10 @@
         <v>46291</v>
       </c>
       <c r="H69" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I69" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>33</v>
@@ -6678,10 +6056,10 @@
         <v>46291</v>
       </c>
       <c r="H70" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I70" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>39</v>
@@ -6716,10 +6094,10 @@
         <v>46291</v>
       </c>
       <c r="H71" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I71" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>199</v>
@@ -6756,10 +6134,10 @@
         <v>46291</v>
       </c>
       <c r="H72" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I72" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>201</v>
@@ -6800,10 +6178,10 @@
         <v>46291</v>
       </c>
       <c r="H73" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I73" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>203</v>
@@ -6840,10 +6218,10 @@
         <v>46291</v>
       </c>
       <c r="H74" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I74" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>205</v>
@@ -6884,10 +6262,10 @@
         <v>46291</v>
       </c>
       <c r="H75" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I75" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>207</v>
@@ -6924,10 +6302,10 @@
         <v>46291</v>
       </c>
       <c r="H76" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I76" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>209</v>
@@ -6968,10 +6346,10 @@
         <v>46291</v>
       </c>
       <c r="H77" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I77" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>211</v>
@@ -7008,10 +6386,10 @@
         <v>46291</v>
       </c>
       <c r="H78" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I78" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>213</v>
@@ -7034,8 +6412,7 @@
     <mergeCell ref="A3:N3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="landscape"/>
-  <headerFooter/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="10" max="1048575" man="1"/>
   </colBreaks>
@@ -7043,20 +6420,19 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A2:N21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="26.8571428571429" customWidth="1"/>
-    <col min="7" max="7" width="11.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="9.71428571428571" customWidth="1"/>
-    <col min="10" max="10" width="16.4285714285714" customWidth="1"/>
-    <col min="13" max="13" width="11.1428571428571" customWidth="1"/>
-    <col min="14" max="14" width="9.71428571428571" customWidth="1"/>
+    <col min="3" max="3" width="26.85546875" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
+    <col min="13" max="13" width="11.140625" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="26.25" spans="1:14">
+    <row r="2" spans="1:14" ht="26.25">
       <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
@@ -7065,27 +6441,27 @@
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="16"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="18"/>
-    </row>
-    <row r="4" ht="19.9" customHeight="1" spans="1:14">
+      <c r="A3" s="44"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="46"/>
+    </row>
+    <row r="4" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="30" t="s">
         <v>214</v>
       </c>
       <c r="D4" s="4"/>
@@ -7104,7 +6480,7 @@
       <c r="M4" s="5"/>
       <c r="N4" s="5"/>
     </row>
-    <row r="5" ht="19.9" customHeight="1" spans="1:14">
+    <row r="5" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A5" s="5"/>
       <c r="B5" s="4" t="s">
         <v>6</v>
@@ -7144,7 +6520,7 @@
       </c>
       <c r="N5" s="5"/>
     </row>
-    <row r="6" ht="19.9" customHeight="1" spans="1:14">
+    <row r="6" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A6" s="14">
         <v>1</v>
       </c>
@@ -7161,14 +6537,14 @@
         <v>24</v>
       </c>
       <c r="F6" s="10"/>
-      <c r="G6" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H6" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I6" s="41">
-        <v>0.354166666666667</v>
+      <c r="G6" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H6" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I6" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J6" s="10" t="s">
         <v>218</v>
@@ -7180,7 +6556,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" ht="19.9" customHeight="1" spans="1:14">
+    <row r="7" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A7" s="14">
         <v>2</v>
       </c>
@@ -7197,14 +6573,14 @@
         <v>18</v>
       </c>
       <c r="F7" s="10"/>
-      <c r="G7" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H7" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I7" s="41">
-        <v>0.354166666666667</v>
+      <c r="G7" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H7" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I7" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J7" s="10" t="s">
         <v>220</v>
@@ -7216,7 +6592,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" ht="19.9" customHeight="1" spans="1:14">
+    <row r="8" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A8" s="14">
         <v>3</v>
       </c>
@@ -7235,14 +6611,14 @@
       <c r="F8" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H8" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I8" s="41">
-        <v>0.354166666666667</v>
+      <c r="G8" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H8" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I8" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J8" s="10" t="s">
         <v>222</v>
@@ -7260,7 +6636,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="9" ht="19.9" customHeight="1" spans="1:14">
+    <row r="9" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A9" s="14">
         <v>4</v>
       </c>
@@ -7277,14 +6653,14 @@
         <v>24</v>
       </c>
       <c r="F9" s="10"/>
-      <c r="G9" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H9" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I9" s="41">
-        <v>0.354166666666667</v>
+      <c r="G9" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H9" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I9" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J9" s="10" t="s">
         <v>224</v>
@@ -7298,7 +6674,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" ht="19.9" customHeight="1" spans="1:14">
+    <row r="10" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A10" s="14">
         <v>5</v>
       </c>
@@ -7317,14 +6693,14 @@
       <c r="F10" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H10" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I10" s="41">
-        <v>0.354166666666667</v>
+      <c r="G10" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H10" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I10" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J10" s="10" t="s">
         <v>226</v>
@@ -7338,7 +6714,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" ht="19.9" customHeight="1" spans="1:14">
+    <row r="11" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A11" s="14">
         <v>6</v>
       </c>
@@ -7355,14 +6731,14 @@
         <v>24</v>
       </c>
       <c r="F11" s="10"/>
-      <c r="G11" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H11" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I11" s="41">
-        <v>0.354166666666667</v>
+      <c r="G11" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H11" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I11" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J11" s="10" t="s">
         <v>228</v>
@@ -7376,7 +6752,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="12" ht="19.9" customHeight="1" spans="1:14">
+    <row r="12" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A12" s="14">
         <v>7</v>
       </c>
@@ -7393,14 +6769,14 @@
         <v>18</v>
       </c>
       <c r="F12" s="10"/>
-      <c r="G12" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H12" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I12" s="41">
-        <v>0.354166666666667</v>
+      <c r="G12" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H12" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I12" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J12" s="10" t="s">
         <v>230</v>
@@ -7414,7 +6790,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" ht="19.9" customHeight="1" spans="1:14">
+    <row r="13" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A13" s="14">
         <v>8</v>
       </c>
@@ -7433,14 +6809,14 @@
       <c r="F13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H13" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I13" s="41">
-        <v>0.354166666666667</v>
+      <c r="G13" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H13" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I13" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J13" s="10" t="s">
         <v>231</v>
@@ -7458,7 +6834,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" ht="19.9" customHeight="1" spans="1:14">
+    <row r="14" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A14" s="14">
         <v>9</v>
       </c>
@@ -7475,14 +6851,14 @@
         <v>24</v>
       </c>
       <c r="F14" s="10"/>
-      <c r="G14" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H14" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I14" s="41">
-        <v>0.354166666666667</v>
+      <c r="G14" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H14" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I14" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J14" s="10" t="s">
         <v>233</v>
@@ -7496,7 +6872,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" ht="19.9" customHeight="1" spans="1:14">
+    <row r="15" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A15" s="14">
         <v>10</v>
       </c>
@@ -7513,14 +6889,14 @@
         <v>18</v>
       </c>
       <c r="F15" s="10"/>
-      <c r="G15" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H15" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I15" s="41">
-        <v>0.354166666666667</v>
+      <c r="G15" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H15" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I15" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J15" s="10" t="s">
         <v>235</v>
@@ -7534,7 +6910,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" ht="19.9" customHeight="1" spans="1:14">
+    <row r="16" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A16" s="14">
         <v>11</v>
       </c>
@@ -7551,14 +6927,14 @@
         <v>24</v>
       </c>
       <c r="F16" s="10"/>
-      <c r="G16" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H16" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I16" s="41">
-        <v>0.354166666666667</v>
+      <c r="G16" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H16" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I16" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J16" s="10" t="s">
         <v>237</v>
@@ -7572,7 +6948,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" ht="19.9" customHeight="1" spans="1:14">
+    <row r="17" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A17" s="14">
         <v>12</v>
       </c>
@@ -7589,14 +6965,14 @@
         <v>18</v>
       </c>
       <c r="F17" s="10"/>
-      <c r="G17" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H17" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I17" s="41">
-        <v>0.354166666666667</v>
+      <c r="G17" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H17" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I17" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J17" s="10" t="s">
         <v>239</v>
@@ -7610,7 +6986,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" ht="19.9" customHeight="1" spans="1:14">
+    <row r="18" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A18" s="14">
         <v>13</v>
       </c>
@@ -7629,14 +7005,14 @@
       <c r="F18" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G18" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H18" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I18" s="41">
-        <v>0.354166666666667</v>
+      <c r="G18" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H18" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I18" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J18" s="10" t="s">
         <v>241</v>
@@ -7654,7 +7030,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" ht="19.9" customHeight="1" spans="1:14">
+    <row r="19" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A19" s="14">
         <v>14</v>
       </c>
@@ -7671,14 +7047,14 @@
         <v>24</v>
       </c>
       <c r="F19" s="10"/>
-      <c r="G19" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H19" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I19" s="41">
-        <v>0.354166666666667</v>
+      <c r="G19" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H19" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I19" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J19" s="10" t="s">
         <v>20</v>
@@ -7692,7 +7068,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" ht="19.9" customHeight="1" spans="1:14">
+    <row r="20" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A20" s="14">
         <v>15</v>
       </c>
@@ -7709,14 +7085,14 @@
         <v>18</v>
       </c>
       <c r="F20" s="10"/>
-      <c r="G20" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H20" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I20" s="41">
-        <v>0.354166666666667</v>
+      <c r="G20" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H20" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I20" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J20" s="10" t="s">
         <v>244</v>
@@ -7730,7 +7106,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="21" ht="19.9" customHeight="1" spans="1:14">
+    <row r="21" spans="1:14" ht="19.899999999999999" customHeight="1">
       <c r="A21" s="14">
         <v>16</v>
       </c>
@@ -7747,14 +7123,14 @@
         <v>24</v>
       </c>
       <c r="F21" s="10"/>
-      <c r="G21" s="40">
-        <v>46291</v>
-      </c>
-      <c r="H21" s="41">
-        <v>0.815972222222222</v>
-      </c>
-      <c r="I21" s="41">
-        <v>0.354166666666667</v>
+      <c r="G21" s="35">
+        <v>46291</v>
+      </c>
+      <c r="H21" s="36">
+        <v>0.81597222222222199</v>
+      </c>
+      <c r="I21" s="36">
+        <v>0.35416666666666702</v>
       </c>
       <c r="J21" s="10" t="s">
         <v>246</v>
@@ -7773,25 +7149,23 @@
     <mergeCell ref="A3:N3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="landscape"/>
-  <headerFooter/>
+  <pageSetup orientation="landscape"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A2:N21"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="7" max="7" width="11.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="9.71428571428571" customWidth="1"/>
-    <col min="10" max="10" width="16.4285714285714" customWidth="1"/>
-    <col min="14" max="14" width="9.71428571428571" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="26.25" spans="1:14">
+    <row r="2" spans="1:14" ht="26.25">
       <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
@@ -7800,27 +7174,27 @@
       <c r="H2" s="3"/>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="16"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="18"/>
+      <c r="A3" s="44"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="46"/>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="5"/>
       <c r="B4" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="35" t="s">
+      <c r="C4" s="30" t="s">
         <v>214</v>
       </c>
       <c r="D4" s="4"/>
@@ -7900,10 +7274,10 @@
         <v>46291</v>
       </c>
       <c r="H6" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I6" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>218</v>
@@ -7936,10 +7310,10 @@
         <v>46291</v>
       </c>
       <c r="H7" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I7" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>220</v>
@@ -7974,10 +7348,10 @@
         <v>46291</v>
       </c>
       <c r="H8" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I8" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>249</v>
@@ -8016,10 +7390,10 @@
         <v>46291</v>
       </c>
       <c r="H9" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I9" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>250</v>
@@ -8054,10 +7428,10 @@
         <v>46291</v>
       </c>
       <c r="H10" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I10" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>251</v>
@@ -8094,10 +7468,10 @@
         <v>46291</v>
       </c>
       <c r="H11" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I11" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>252</v>
@@ -8132,10 +7506,10 @@
         <v>46291</v>
       </c>
       <c r="H12" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I12" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>253</v>
@@ -8172,10 +7546,10 @@
         <v>46291</v>
       </c>
       <c r="H13" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I13" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>254</v>
@@ -8214,10 +7588,10 @@
         <v>46291</v>
       </c>
       <c r="H14" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I14" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>255</v>
@@ -8252,10 +7626,10 @@
         <v>46291</v>
       </c>
       <c r="H15" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I15" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>256</v>
@@ -8290,10 +7664,10 @@
         <v>46291</v>
       </c>
       <c r="H16" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I16" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>257</v>
@@ -8328,10 +7702,10 @@
         <v>46291</v>
       </c>
       <c r="H17" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I17" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>258</v>
@@ -8366,10 +7740,10 @@
         <v>46291</v>
       </c>
       <c r="H18" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I18" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>259</v>
@@ -8404,10 +7778,10 @@
         <v>46291</v>
       </c>
       <c r="H19" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I19" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>260</v>
@@ -8442,10 +7816,10 @@
         <v>46291</v>
       </c>
       <c r="H20" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I20" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>261</v>
@@ -8482,10 +7856,10 @@
         <v>46291</v>
       </c>
       <c r="H21" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I21" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>262</v>
@@ -8508,24 +7882,22 @@
     <mergeCell ref="A3:N3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A2:N384"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="21" customWidth="1"/>
-    <col min="7" max="7" width="11.1428571428571" customWidth="1"/>
-    <col min="8" max="8" width="9.71428571428571" customWidth="1"/>
-    <col min="10" max="10" width="16.4285714285714" customWidth="1"/>
-    <col min="14" max="14" width="9.71428571428571" customWidth="1"/>
+    <col min="7" max="7" width="11.140625" customWidth="1"/>
+    <col min="8" max="8" width="9.7109375" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="26.25" spans="1:14">
+    <row r="2" spans="1:14" ht="26.25">
       <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
@@ -8533,7 +7905,7 @@
       <c r="G2" s="2"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" ht="26.25" spans="1:14">
+    <row r="3" spans="1:14" ht="26.25">
       <c r="A3" s="5"/>
       <c r="B3" s="4" t="s">
         <v>1</v>
@@ -8624,7 +7996,7 @@
         <v>46290</v>
       </c>
       <c r="H5" s="9">
-        <v>0.475694444444444</v>
+        <v>0.47569444444444398</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>269</v>
@@ -8668,7 +8040,7 @@
         <v>46290</v>
       </c>
       <c r="H6" s="9">
-        <v>0.475694444444444</v>
+        <v>0.47569444444444398</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>272</v>
@@ -8688,22 +8060,22 @@
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="16"/>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="17"/>
-      <c r="L7" s="17"/>
-      <c r="M7" s="17"/>
-      <c r="N7" s="18"/>
-    </row>
-    <row r="8" ht="26.25" spans="1:14">
+      <c r="A7" s="44"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="45"/>
+      <c r="F7" s="45"/>
+      <c r="G7" s="45"/>
+      <c r="H7" s="45"/>
+      <c r="I7" s="45"/>
+      <c r="J7" s="45"/>
+      <c r="K7" s="45"/>
+      <c r="L7" s="45"/>
+      <c r="M7" s="45"/>
+      <c r="N7" s="46"/>
+    </row>
+    <row r="8" spans="1:14" ht="26.25">
       <c r="A8" s="5"/>
       <c r="B8" s="4" t="s">
         <v>1</v>
@@ -8837,7 +8209,7 @@
         <v>0.211805555555556</v>
       </c>
       <c r="I11" s="9">
-        <v>0.472222222222222</v>
+        <v>0.47222222222222199</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>277</v>
@@ -8852,22 +8224,22 @@
       </c>
     </row>
     <row r="12" spans="1:14">
-      <c r="A12" s="16"/>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="17"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="17"/>
-      <c r="N12" s="18"/>
-    </row>
-    <row r="13" ht="26.25" spans="1:14">
+      <c r="A12" s="44"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
+      <c r="K12" s="45"/>
+      <c r="L12" s="45"/>
+      <c r="M12" s="45"/>
+      <c r="N12" s="46"/>
+    </row>
+    <row r="13" spans="1:14" ht="26.25">
       <c r="A13" s="5"/>
       <c r="B13" s="4" t="s">
         <v>1</v>
@@ -8956,7 +8328,7 @@
         <v>46291</v>
       </c>
       <c r="H15" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I15" s="12" t="s">
         <v>279</v>
@@ -9000,7 +8372,7 @@
         <v>46291</v>
       </c>
       <c r="H16" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I16" s="12" t="s">
         <v>281</v>
@@ -9040,7 +8412,7 @@
         <v>46291</v>
       </c>
       <c r="H17" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I17" s="12" t="s">
         <v>279</v>
@@ -9080,7 +8452,7 @@
         <v>46291</v>
       </c>
       <c r="H18" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I18" s="12" t="s">
         <v>281</v>
@@ -9098,22 +8470,22 @@
       </c>
     </row>
     <row r="19" spans="1:14">
-      <c r="A19" s="16"/>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-      <c r="I19" s="17"/>
-      <c r="J19" s="17"/>
-      <c r="K19" s="17"/>
-      <c r="L19" s="17"/>
-      <c r="M19" s="17"/>
-      <c r="N19" s="18"/>
-    </row>
-    <row r="20" ht="26.25" spans="1:14">
+      <c r="A19" s="44"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
+      <c r="G19" s="45"/>
+      <c r="H19" s="45"/>
+      <c r="I19" s="45"/>
+      <c r="J19" s="45"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="45"/>
+      <c r="M19" s="45"/>
+      <c r="N19" s="46"/>
+    </row>
+    <row r="20" spans="1:14" ht="26.25">
       <c r="A20" s="5"/>
       <c r="B20" s="4" t="s">
         <v>1</v>
@@ -9202,7 +8574,7 @@
         <v>46291</v>
       </c>
       <c r="H22" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I22" s="12" t="s">
         <v>128</v>
@@ -9246,7 +8618,7 @@
         <v>46291</v>
       </c>
       <c r="H23" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I23" s="12" t="s">
         <v>128</v>
@@ -9286,7 +8658,7 @@
         <v>46291</v>
       </c>
       <c r="H24" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I24" s="12" t="s">
         <v>128</v>
@@ -9326,7 +8698,7 @@
         <v>46291</v>
       </c>
       <c r="H25" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I25" s="12" t="s">
         <v>128</v>
@@ -9344,22 +8716,22 @@
       </c>
     </row>
     <row r="26" spans="1:14">
-      <c r="A26" s="16"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="17"/>
-      <c r="F26" s="17"/>
-      <c r="G26" s="17"/>
-      <c r="H26" s="17"/>
-      <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
-      <c r="K26" s="17"/>
-      <c r="L26" s="17"/>
-      <c r="M26" s="17"/>
-      <c r="N26" s="18"/>
-    </row>
-    <row r="27" ht="26.25" spans="1:14">
+      <c r="A26" s="44"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
+      <c r="D26" s="45"/>
+      <c r="E26" s="45"/>
+      <c r="F26" s="45"/>
+      <c r="G26" s="45"/>
+      <c r="H26" s="45"/>
+      <c r="I26" s="45"/>
+      <c r="J26" s="45"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="45"/>
+      <c r="M26" s="45"/>
+      <c r="N26" s="46"/>
+    </row>
+    <row r="27" spans="1:14" ht="26.25">
       <c r="A27" s="5"/>
       <c r="B27" s="4" t="s">
         <v>1</v>
@@ -9371,10 +8743,10 @@
       <c r="E27" s="7"/>
       <c r="F27" s="8"/>
       <c r="G27" s="6"/>
-      <c r="H27" s="19" t="s">
+      <c r="H27" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="I27" s="19" t="s">
+      <c r="I27" s="16" t="s">
         <v>3</v>
       </c>
       <c r="J27" s="5"/>
@@ -9450,7 +8822,7 @@
       <c r="H29" s="5">
         <v>11.25</v>
       </c>
-      <c r="I29" s="20">
+      <c r="I29" s="17">
         <v>4.5</v>
       </c>
       <c r="J29" s="5" t="s">
@@ -9494,7 +8866,7 @@
       <c r="H30" s="5">
         <v>11.25</v>
       </c>
-      <c r="I30" s="20">
+      <c r="I30" s="17">
         <v>4.5</v>
       </c>
       <c r="J30" s="5" t="s">
@@ -9534,7 +8906,7 @@
       <c r="H31" s="5">
         <v>11.25</v>
       </c>
-      <c r="I31" s="20">
+      <c r="I31" s="17">
         <v>4.5</v>
       </c>
       <c r="J31" s="5" t="s">
@@ -9574,7 +8946,7 @@
       <c r="H32" s="5">
         <v>11.25</v>
       </c>
-      <c r="I32" s="20">
+      <c r="I32" s="17">
         <v>4.5</v>
       </c>
       <c r="J32" s="5" t="s">
@@ -9614,7 +8986,7 @@
       <c r="H33" s="5">
         <v>11.25</v>
       </c>
-      <c r="I33" s="20">
+      <c r="I33" s="17">
         <v>4.5</v>
       </c>
       <c r="J33" s="5" t="s">
@@ -9654,7 +9026,7 @@
       <c r="H34" s="5">
         <v>11.25</v>
       </c>
-      <c r="I34" s="20">
+      <c r="I34" s="17">
         <v>4.5</v>
       </c>
       <c r="J34" s="5" t="s">
@@ -9670,22 +9042,22 @@
       </c>
     </row>
     <row r="35" spans="1:14">
-      <c r="A35" s="21"/>
-      <c r="B35" s="22"/>
-      <c r="C35" s="22"/>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="22"/>
-      <c r="N35" s="22"/>
-    </row>
-    <row r="36" ht="26.25" spans="1:14">
+      <c r="A35" s="47"/>
+      <c r="B35" s="48"/>
+      <c r="C35" s="48"/>
+      <c r="D35" s="48"/>
+      <c r="E35" s="48"/>
+      <c r="F35" s="48"/>
+      <c r="G35" s="48"/>
+      <c r="H35" s="48"/>
+      <c r="I35" s="48"/>
+      <c r="J35" s="48"/>
+      <c r="K35" s="48"/>
+      <c r="L35" s="48"/>
+      <c r="M35" s="48"/>
+      <c r="N35" s="48"/>
+    </row>
+    <row r="36" spans="1:14" ht="26.25">
       <c r="A36" s="5"/>
       <c r="B36" s="4" t="s">
         <v>1</v>
@@ -9776,7 +9148,7 @@
       <c r="H38" s="5">
         <v>5.05</v>
       </c>
-      <c r="I38" s="20">
+      <c r="I38" s="17">
         <v>11.2</v>
       </c>
       <c r="J38" s="5" t="s">
@@ -9820,7 +9192,7 @@
       <c r="H39" s="5">
         <v>5.05</v>
       </c>
-      <c r="I39" s="20">
+      <c r="I39" s="17">
         <v>11.2</v>
       </c>
       <c r="J39" s="5" t="s">
@@ -9860,7 +9232,7 @@
       <c r="H40" s="5">
         <v>5.05</v>
       </c>
-      <c r="I40" s="20">
+      <c r="I40" s="17">
         <v>11.2</v>
       </c>
       <c r="J40" s="5" t="s">
@@ -9900,7 +9272,7 @@
       <c r="H41" s="5">
         <v>5.05</v>
       </c>
-      <c r="I41" s="20">
+      <c r="I41" s="17">
         <v>11.2</v>
       </c>
       <c r="J41" s="5" t="s">
@@ -9940,7 +9312,7 @@
       <c r="H42" s="5">
         <v>5.05</v>
       </c>
-      <c r="I42" s="20">
+      <c r="I42" s="17">
         <v>11.2</v>
       </c>
       <c r="J42" s="5" t="s">
@@ -9980,7 +9352,7 @@
       <c r="H43" s="5">
         <v>5.05</v>
       </c>
-      <c r="I43" s="20">
+      <c r="I43" s="17">
         <v>11.2</v>
       </c>
       <c r="J43" s="5" t="s">
@@ -9996,22 +9368,22 @@
       </c>
     </row>
     <row r="44" spans="1:14">
-      <c r="A44" s="21"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="22"/>
-      <c r="H44" s="22"/>
-      <c r="I44" s="22"/>
-      <c r="J44" s="22"/>
-      <c r="K44" s="22"/>
-      <c r="L44" s="22"/>
-      <c r="M44" s="22"/>
-      <c r="N44" s="23"/>
-    </row>
-    <row r="45" ht="26.25" spans="1:14">
+      <c r="A44" s="47"/>
+      <c r="B44" s="48"/>
+      <c r="C44" s="48"/>
+      <c r="D44" s="48"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="48"/>
+      <c r="I44" s="48"/>
+      <c r="J44" s="48"/>
+      <c r="K44" s="48"/>
+      <c r="L44" s="48"/>
+      <c r="M44" s="48"/>
+      <c r="N44" s="49"/>
+    </row>
+    <row r="45" spans="1:14" ht="26.25">
       <c r="A45" s="5"/>
       <c r="B45" s="4" t="s">
         <v>1</v>
@@ -10100,7 +9472,7 @@
       <c r="H47" s="5">
         <v>11.25</v>
       </c>
-      <c r="I47" s="24">
+      <c r="I47" s="19">
         <v>4.5</v>
       </c>
       <c r="J47" s="5" t="s">
@@ -10144,7 +9516,7 @@
       <c r="H48" s="5">
         <v>11.25</v>
       </c>
-      <c r="I48" s="24">
+      <c r="I48" s="19">
         <v>4.5</v>
       </c>
       <c r="J48" s="5" t="s">
@@ -10184,7 +9556,7 @@
       <c r="H49" s="5">
         <v>11.25</v>
       </c>
-      <c r="I49" s="24">
+      <c r="I49" s="19">
         <v>4.5</v>
       </c>
       <c r="J49" s="5" t="s">
@@ -10224,7 +9596,7 @@
       <c r="H50" s="5">
         <v>11.25</v>
       </c>
-      <c r="I50" s="24">
+      <c r="I50" s="19">
         <v>4.5</v>
       </c>
       <c r="J50" s="5" t="s">
@@ -10264,7 +9636,7 @@
       <c r="H51" s="5">
         <v>11.25</v>
       </c>
-      <c r="I51" s="24">
+      <c r="I51" s="19">
         <v>4.5</v>
       </c>
       <c r="J51" s="5" t="s">
@@ -10280,84 +9652,84 @@
       </c>
     </row>
     <row r="52" spans="1:14">
-      <c r="A52" s="25">
+      <c r="A52" s="20">
         <v>6</v>
       </c>
       <c r="B52" s="14">
         <v>19031</v>
       </c>
-      <c r="C52" s="26" t="s">
+      <c r="C52" s="21" t="s">
         <v>46</v>
       </c>
-      <c r="D52" s="27">
+      <c r="D52" s="22">
         <v>15</v>
       </c>
-      <c r="E52" s="27" t="s">
-        <v>24</v>
-      </c>
-      <c r="F52" s="27" t="s">
+      <c r="E52" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="F52" s="22" t="s">
         <v>19</v>
       </c>
-      <c r="G52" s="28">
-        <v>46291</v>
-      </c>
-      <c r="H52" s="25">
+      <c r="G52" s="23">
+        <v>46291</v>
+      </c>
+      <c r="H52" s="20">
         <v>11.25</v>
       </c>
-      <c r="I52" s="29">
+      <c r="I52" s="24">
         <v>4.5</v>
       </c>
-      <c r="J52" s="25" t="s">
+      <c r="J52" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="K52" s="25"/>
-      <c r="L52" s="25"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
       <c r="M52" s="5">
         <v>15917554</v>
       </c>
-      <c r="N52" s="25">
+      <c r="N52" s="20">
         <v>4</v>
       </c>
     </row>
     <row r="53" spans="1:14">
-      <c r="A53" s="16"/>
-      <c r="B53" s="17"/>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="17"/>
-      <c r="H53" s="17"/>
-      <c r="I53" s="17"/>
-      <c r="J53" s="17"/>
-      <c r="K53" s="17"/>
-      <c r="L53" s="17"/>
-      <c r="M53" s="17"/>
-      <c r="N53" s="18"/>
-    </row>
-    <row r="54" ht="26.25" spans="1:14">
-      <c r="A54" s="30"/>
-      <c r="B54" s="31" t="s">
+      <c r="A53" s="44"/>
+      <c r="B53" s="45"/>
+      <c r="C53" s="45"/>
+      <c r="D53" s="45"/>
+      <c r="E53" s="45"/>
+      <c r="F53" s="45"/>
+      <c r="G53" s="45"/>
+      <c r="H53" s="45"/>
+      <c r="I53" s="45"/>
+      <c r="J53" s="45"/>
+      <c r="K53" s="45"/>
+      <c r="L53" s="45"/>
+      <c r="M53" s="45"/>
+      <c r="N53" s="46"/>
+    </row>
+    <row r="54" spans="1:14" ht="26.25">
+      <c r="A54" s="25"/>
+      <c r="B54" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C54" s="31" t="s">
+      <c r="C54" s="26" t="s">
         <v>287</v>
       </c>
-      <c r="D54" s="31"/>
-      <c r="E54" s="32"/>
-      <c r="F54" s="33"/>
-      <c r="G54" s="34"/>
-      <c r="H54" s="30" t="s">
+      <c r="D54" s="26"/>
+      <c r="E54" s="27"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="29"/>
+      <c r="H54" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="I54" s="30" t="s">
+      <c r="I54" s="25" t="s">
         <v>288</v>
       </c>
-      <c r="J54" s="30"/>
-      <c r="K54" s="30"/>
-      <c r="L54" s="30"/>
-      <c r="M54" s="30"/>
-      <c r="N54" s="30"/>
+      <c r="J54" s="25"/>
+      <c r="K54" s="25"/>
+      <c r="L54" s="25"/>
+      <c r="M54" s="25"/>
+      <c r="N54" s="25"/>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="5"/>
@@ -10424,7 +9796,7 @@
       <c r="H56" s="5">
         <v>5.05</v>
       </c>
-      <c r="I56" s="24">
+      <c r="I56" s="19">
         <v>11.2</v>
       </c>
       <c r="J56" s="5" t="s">
@@ -10468,7 +9840,7 @@
       <c r="H57" s="5">
         <v>5.05</v>
       </c>
-      <c r="I57" s="24">
+      <c r="I57" s="19">
         <v>11.2</v>
       </c>
       <c r="J57" s="5" t="s">
@@ -10508,7 +9880,7 @@
       <c r="H58" s="5">
         <v>5.05</v>
       </c>
-      <c r="I58" s="24">
+      <c r="I58" s="19">
         <v>11.2</v>
       </c>
       <c r="J58" s="5" t="s">
@@ -10548,7 +9920,7 @@
       <c r="H59" s="5">
         <v>5.05</v>
       </c>
-      <c r="I59" s="24">
+      <c r="I59" s="19">
         <v>11.2</v>
       </c>
       <c r="J59" s="5" t="s">
@@ -10588,7 +9960,7 @@
       <c r="H60" s="5">
         <v>5.05</v>
       </c>
-      <c r="I60" s="24">
+      <c r="I60" s="19">
         <v>11.2</v>
       </c>
       <c r="J60" s="5" t="s">
@@ -10628,7 +10000,7 @@
       <c r="H61" s="5">
         <v>5.05</v>
       </c>
-      <c r="I61" s="24">
+      <c r="I61" s="19">
         <v>11.2</v>
       </c>
       <c r="J61" s="5" t="s">
@@ -10644,27 +10016,27 @@
       </c>
     </row>
     <row r="62" spans="1:14">
-      <c r="A62" s="17"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="17"/>
-      <c r="D62" s="17"/>
-      <c r="E62" s="17"/>
-      <c r="F62" s="17"/>
-      <c r="G62" s="17"/>
-      <c r="H62" s="17"/>
-      <c r="I62" s="17"/>
-      <c r="J62" s="17"/>
-      <c r="K62" s="17"/>
-      <c r="L62" s="17"/>
-      <c r="M62" s="17"/>
-      <c r="N62" s="17"/>
-    </row>
-    <row r="63" ht="26.25" spans="1:14">
+      <c r="A62" s="45"/>
+      <c r="B62" s="45"/>
+      <c r="C62" s="45"/>
+      <c r="D62" s="45"/>
+      <c r="E62" s="45"/>
+      <c r="F62" s="45"/>
+      <c r="G62" s="45"/>
+      <c r="H62" s="45"/>
+      <c r="I62" s="45"/>
+      <c r="J62" s="45"/>
+      <c r="K62" s="45"/>
+      <c r="L62" s="45"/>
+      <c r="M62" s="45"/>
+      <c r="N62" s="45"/>
+    </row>
+    <row r="63" spans="1:14" ht="26.25">
       <c r="A63" s="5"/>
       <c r="B63" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C63" s="35" t="s">
+      <c r="C63" s="30" t="s">
         <v>21</v>
       </c>
       <c r="D63" s="4"/>
@@ -10746,10 +10118,10 @@
         <v>46291</v>
       </c>
       <c r="H65" s="9">
-        <v>0.475694444444444</v>
+        <v>0.47569444444444398</v>
       </c>
       <c r="I65" s="9">
-        <v>0.201388888888889</v>
+        <v>0.20138888888888901</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>65</v>
@@ -10790,10 +10162,10 @@
         <v>46291</v>
       </c>
       <c r="H66" s="9">
-        <v>0.475694444444444</v>
+        <v>0.47569444444444398</v>
       </c>
       <c r="I66" s="9">
-        <v>0.201388888888889</v>
+        <v>0.20138888888888901</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>66</v>
@@ -10830,10 +10202,10 @@
         <v>46291</v>
       </c>
       <c r="H67" s="9">
-        <v>0.475694444444444</v>
+        <v>0.47569444444444398</v>
       </c>
       <c r="I67" s="9">
-        <v>0.201388888888889</v>
+        <v>0.20138888888888901</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>67</v>
@@ -10870,10 +10242,10 @@
         <v>46291</v>
       </c>
       <c r="H68" s="9">
-        <v>0.475694444444444</v>
+        <v>0.47569444444444398</v>
       </c>
       <c r="I68" s="9">
-        <v>0.201388888888889</v>
+        <v>0.20138888888888901</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>68</v>
@@ -10910,10 +10282,10 @@
         <v>46291</v>
       </c>
       <c r="H69" s="9">
-        <v>0.475694444444444</v>
+        <v>0.47569444444444398</v>
       </c>
       <c r="I69" s="9">
-        <v>0.201388888888889</v>
+        <v>0.20138888888888901</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>63</v>
@@ -10950,10 +10322,10 @@
         <v>46291</v>
       </c>
       <c r="H70" s="9">
-        <v>0.475694444444444</v>
+        <v>0.47569444444444398</v>
       </c>
       <c r="I70" s="9">
-        <v>0.201388888888889</v>
+        <v>0.20138888888888901</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>64</v>
@@ -10968,27 +10340,27 @@
       </c>
     </row>
     <row r="71" spans="1:14">
-      <c r="A71" s="22"/>
-      <c r="B71" s="22"/>
-      <c r="C71" s="22"/>
-      <c r="D71" s="22"/>
-      <c r="E71" s="22"/>
-      <c r="F71" s="22"/>
-      <c r="G71" s="22"/>
-      <c r="H71" s="22"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="22"/>
-      <c r="K71" s="22"/>
-      <c r="L71" s="22"/>
-      <c r="M71" s="22"/>
-      <c r="N71" s="22"/>
-    </row>
-    <row r="72" ht="26.25" spans="1:14">
+      <c r="A71" s="48"/>
+      <c r="B71" s="48"/>
+      <c r="C71" s="48"/>
+      <c r="D71" s="48"/>
+      <c r="E71" s="48"/>
+      <c r="F71" s="48"/>
+      <c r="G71" s="48"/>
+      <c r="H71" s="48"/>
+      <c r="I71" s="48"/>
+      <c r="J71" s="48"/>
+      <c r="K71" s="48"/>
+      <c r="L71" s="48"/>
+      <c r="M71" s="48"/>
+      <c r="N71" s="48"/>
+    </row>
+    <row r="72" spans="1:14" ht="26.25">
       <c r="A72" s="5"/>
       <c r="B72" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C72" s="35" t="s">
+      <c r="C72" s="30" t="s">
         <v>21</v>
       </c>
       <c r="D72" s="4"/>
@@ -11073,7 +10445,7 @@
         <v>0.211805555555556</v>
       </c>
       <c r="I74" s="9">
-        <v>0.472222222222222</v>
+        <v>0.47222222222222199</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>22</v>
@@ -11117,7 +10489,7 @@
         <v>0.211805555555556</v>
       </c>
       <c r="I75" s="9">
-        <v>0.472222222222222</v>
+        <v>0.47222222222222199</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>20</v>
@@ -11157,7 +10529,7 @@
         <v>0.211805555555556</v>
       </c>
       <c r="I76" s="9">
-        <v>0.472222222222222</v>
+        <v>0.47222222222222199</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>27</v>
@@ -11197,7 +10569,7 @@
         <v>0.211805555555556</v>
       </c>
       <c r="I77" s="9">
-        <v>0.472222222222222</v>
+        <v>0.47222222222222199</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>29</v>
@@ -11237,7 +10609,7 @@
         <v>0.211805555555556</v>
       </c>
       <c r="I78" s="9">
-        <v>0.472222222222222</v>
+        <v>0.47222222222222199</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>31</v>
@@ -11277,7 +10649,7 @@
         <v>0.211805555555556</v>
       </c>
       <c r="I79" s="9">
-        <v>0.472222222222222</v>
+        <v>0.47222222222222199</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>25</v>
@@ -11292,27 +10664,27 @@
       </c>
     </row>
     <row r="80" spans="1:14">
-      <c r="A80" s="17"/>
-      <c r="B80" s="17"/>
-      <c r="C80" s="17"/>
-      <c r="D80" s="17"/>
-      <c r="E80" s="17"/>
-      <c r="F80" s="17"/>
-      <c r="G80" s="17"/>
-      <c r="H80" s="17"/>
-      <c r="I80" s="17"/>
-      <c r="J80" s="17"/>
-      <c r="K80" s="17"/>
-      <c r="L80" s="17"/>
-      <c r="M80" s="17"/>
-      <c r="N80" s="17"/>
-    </row>
-    <row r="81" ht="26.25" spans="1:14">
+      <c r="A80" s="45"/>
+      <c r="B80" s="45"/>
+      <c r="C80" s="45"/>
+      <c r="D80" s="45"/>
+      <c r="E80" s="45"/>
+      <c r="F80" s="45"/>
+      <c r="G80" s="45"/>
+      <c r="H80" s="45"/>
+      <c r="I80" s="45"/>
+      <c r="J80" s="45"/>
+      <c r="K80" s="45"/>
+      <c r="L80" s="45"/>
+      <c r="M80" s="45"/>
+      <c r="N80" s="45"/>
+    </row>
+    <row r="81" spans="1:14" ht="26.25">
       <c r="A81" s="5"/>
       <c r="B81" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C81" s="35" t="s">
+      <c r="C81" s="30" t="s">
         <v>138</v>
       </c>
       <c r="D81" s="4"/>
@@ -11394,10 +10766,10 @@
         <v>46291</v>
       </c>
       <c r="H83" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I83" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>291</v>
@@ -11438,10 +10810,10 @@
         <v>46291</v>
       </c>
       <c r="H84" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I84" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J84" s="5" t="s">
         <v>292</v>
@@ -11476,10 +10848,10 @@
         <v>46291</v>
       </c>
       <c r="H85" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I85" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J85" s="5" t="s">
         <v>293</v>
@@ -11514,10 +10886,10 @@
         <v>46291</v>
       </c>
       <c r="H86" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I86" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J86" s="5" t="s">
         <v>294</v>
@@ -11552,10 +10924,10 @@
         <v>46291</v>
       </c>
       <c r="H87" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I87" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J87" s="5" t="s">
         <v>295</v>
@@ -11590,10 +10962,10 @@
         <v>46291</v>
       </c>
       <c r="H88" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I88" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>296</v>
@@ -11608,27 +10980,27 @@
       </c>
     </row>
     <row r="89" spans="1:14">
-      <c r="A89" s="22"/>
-      <c r="B89" s="22"/>
-      <c r="C89" s="36"/>
-      <c r="D89" s="22"/>
-      <c r="E89" s="22"/>
-      <c r="F89" s="37"/>
-      <c r="G89" s="38"/>
-      <c r="H89" s="39"/>
-      <c r="I89" s="39"/>
-      <c r="J89" s="37"/>
-      <c r="K89" s="37"/>
-      <c r="L89" s="37"/>
-      <c r="M89" s="37"/>
-      <c r="N89" s="37"/>
-    </row>
-    <row r="90" ht="26.25" spans="1:14">
+      <c r="A89" s="18"/>
+      <c r="B89" s="18"/>
+      <c r="C89" s="31"/>
+      <c r="D89" s="18"/>
+      <c r="E89" s="18"/>
+      <c r="F89" s="32"/>
+      <c r="G89" s="33"/>
+      <c r="H89" s="34"/>
+      <c r="I89" s="34"/>
+      <c r="J89" s="32"/>
+      <c r="K89" s="32"/>
+      <c r="L89" s="32"/>
+      <c r="M89" s="32"/>
+      <c r="N89" s="32"/>
+    </row>
+    <row r="90" spans="1:14" ht="26.25">
       <c r="A90" s="5"/>
       <c r="B90" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C90" s="35" t="s">
+      <c r="C90" s="30" t="s">
         <v>138</v>
       </c>
       <c r="D90" s="4"/>
@@ -11710,10 +11082,10 @@
         <v>46291</v>
       </c>
       <c r="H92" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I92" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J92" s="5" t="s">
         <v>139</v>
@@ -11754,10 +11126,10 @@
         <v>46291</v>
       </c>
       <c r="H93" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I93" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J93" s="5" t="s">
         <v>141</v>
@@ -11794,10 +11166,10 @@
         <v>46291</v>
       </c>
       <c r="H94" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I94" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J94" s="5" t="s">
         <v>25</v>
@@ -11836,10 +11208,10 @@
         <v>46291</v>
       </c>
       <c r="H95" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I95" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J95" s="5" t="s">
         <v>147</v>
@@ -11876,10 +11248,10 @@
         <v>46291</v>
       </c>
       <c r="H96" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I96" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J96" s="5" t="s">
         <v>185</v>
@@ -11916,10 +11288,10 @@
         <v>46291</v>
       </c>
       <c r="H97" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I97" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J97" s="5" t="s">
         <v>187</v>
@@ -11936,27 +11308,27 @@
       </c>
     </row>
     <row r="98" spans="1:14">
-      <c r="A98" s="21"/>
-      <c r="B98" s="22"/>
-      <c r="C98" s="22"/>
-      <c r="D98" s="22"/>
-      <c r="E98" s="22"/>
-      <c r="F98" s="22"/>
-      <c r="G98" s="22"/>
-      <c r="H98" s="22"/>
-      <c r="I98" s="22"/>
-      <c r="J98" s="22"/>
-      <c r="K98" s="22"/>
-      <c r="L98" s="22"/>
-      <c r="M98" s="22"/>
-      <c r="N98" s="23"/>
+      <c r="A98" s="47"/>
+      <c r="B98" s="48"/>
+      <c r="C98" s="48"/>
+      <c r="D98" s="48"/>
+      <c r="E98" s="48"/>
+      <c r="F98" s="48"/>
+      <c r="G98" s="48"/>
+      <c r="H98" s="48"/>
+      <c r="I98" s="48"/>
+      <c r="J98" s="48"/>
+      <c r="K98" s="48"/>
+      <c r="L98" s="48"/>
+      <c r="M98" s="48"/>
+      <c r="N98" s="49"/>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="4"/>
       <c r="B99" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C99" s="35" t="s">
+      <c r="C99" s="30" t="s">
         <v>166</v>
       </c>
       <c r="D99" s="4"/>
@@ -12036,10 +11408,10 @@
         <v>46291</v>
       </c>
       <c r="H101" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I101" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J101" s="5" t="s">
         <v>250</v>
@@ -12078,10 +11450,10 @@
         <v>46291</v>
       </c>
       <c r="H102" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I102" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J102" s="5" t="s">
         <v>251</v>
@@ -12118,10 +11490,10 @@
         <v>46291</v>
       </c>
       <c r="H103" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I103" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J103" s="5" t="s">
         <v>249</v>
@@ -12158,10 +11530,10 @@
         <v>46291</v>
       </c>
       <c r="H104" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I104" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J104" s="5" t="s">
         <v>252</v>
@@ -12196,10 +11568,10 @@
         <v>46291</v>
       </c>
       <c r="H105" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I105" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J105" s="5" t="s">
         <v>297</v>
@@ -12234,10 +11606,10 @@
         <v>46291</v>
       </c>
       <c r="H106" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I106" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J106" s="5" t="s">
         <v>253</v>
@@ -12256,7 +11628,7 @@
       <c r="B108" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C108" s="35" t="s">
+      <c r="C108" s="30" t="s">
         <v>166</v>
       </c>
       <c r="D108" s="4"/>
@@ -12336,10 +11708,10 @@
         <v>46291</v>
       </c>
       <c r="H110" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I110" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J110" s="5" t="s">
         <v>167</v>
@@ -12378,10 +11750,10 @@
         <v>46291</v>
       </c>
       <c r="H111" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I111" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J111" s="5" t="s">
         <v>169</v>
@@ -12418,10 +11790,10 @@
         <v>46291</v>
       </c>
       <c r="H112" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I112" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J112" s="5" t="s">
         <v>165</v>
@@ -12458,10 +11830,10 @@
         <v>46291</v>
       </c>
       <c r="H113" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I113" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J113" s="5" t="s">
         <v>171</v>
@@ -12496,10 +11868,10 @@
         <v>46291</v>
       </c>
       <c r="H114" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I114" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J114" s="5" t="s">
         <v>175</v>
@@ -12534,10 +11906,10 @@
         <v>46291</v>
       </c>
       <c r="H115" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I115" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J115" s="5" t="s">
         <v>173</v>
@@ -12550,27 +11922,27 @@
       <c r="N115" s="5"/>
     </row>
     <row r="116" spans="1:14">
-      <c r="A116" s="17"/>
-      <c r="B116" s="17"/>
-      <c r="C116" s="17"/>
-      <c r="D116" s="17"/>
-      <c r="E116" s="17"/>
-      <c r="F116" s="17"/>
-      <c r="G116" s="17"/>
-      <c r="H116" s="17"/>
-      <c r="I116" s="17"/>
-      <c r="J116" s="17"/>
-      <c r="K116" s="17"/>
-      <c r="L116" s="17"/>
-      <c r="M116" s="17"/>
-      <c r="N116" s="17"/>
+      <c r="A116" s="45"/>
+      <c r="B116" s="45"/>
+      <c r="C116" s="45"/>
+      <c r="D116" s="45"/>
+      <c r="E116" s="45"/>
+      <c r="F116" s="45"/>
+      <c r="G116" s="45"/>
+      <c r="H116" s="45"/>
+      <c r="I116" s="45"/>
+      <c r="J116" s="45"/>
+      <c r="K116" s="45"/>
+      <c r="L116" s="45"/>
+      <c r="M116" s="45"/>
+      <c r="N116" s="45"/>
     </row>
     <row r="117" spans="1:14">
       <c r="A117" s="5"/>
       <c r="B117" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C117" s="35" t="s">
+      <c r="C117" s="30" t="s">
         <v>70</v>
       </c>
       <c r="D117" s="4"/>
@@ -12650,10 +12022,10 @@
         <v>46291</v>
       </c>
       <c r="H119" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I119" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J119" s="5" t="s">
         <v>298</v>
@@ -12692,10 +12064,10 @@
         <v>46291</v>
       </c>
       <c r="H120" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I120" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J120" s="5" t="s">
         <v>299</v>
@@ -12732,10 +12104,10 @@
         <v>46291</v>
       </c>
       <c r="H121" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I121" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J121" s="5" t="s">
         <v>300</v>
@@ -12772,10 +12144,10 @@
         <v>46291</v>
       </c>
       <c r="H122" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I122" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J122" s="5" t="s">
         <v>301</v>
@@ -12810,10 +12182,10 @@
         <v>46291</v>
       </c>
       <c r="H123" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I123" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J123" s="5" t="s">
         <v>302</v>
@@ -12848,10 +12220,10 @@
         <v>46291</v>
       </c>
       <c r="H124" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I124" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J124" s="5" t="s">
         <v>187</v>
@@ -12866,27 +12238,27 @@
       </c>
     </row>
     <row r="125" spans="1:14">
-      <c r="A125" s="17"/>
-      <c r="B125" s="17"/>
-      <c r="C125" s="17"/>
-      <c r="D125" s="17"/>
-      <c r="E125" s="17"/>
-      <c r="F125" s="17"/>
-      <c r="G125" s="17"/>
-      <c r="H125" s="17"/>
-      <c r="I125" s="17"/>
-      <c r="J125" s="17"/>
-      <c r="K125" s="17"/>
-      <c r="L125" s="17"/>
-      <c r="M125" s="17"/>
-      <c r="N125" s="17"/>
+      <c r="A125" s="45"/>
+      <c r="B125" s="45"/>
+      <c r="C125" s="45"/>
+      <c r="D125" s="45"/>
+      <c r="E125" s="45"/>
+      <c r="F125" s="45"/>
+      <c r="G125" s="45"/>
+      <c r="H125" s="45"/>
+      <c r="I125" s="45"/>
+      <c r="J125" s="45"/>
+      <c r="K125" s="45"/>
+      <c r="L125" s="45"/>
+      <c r="M125" s="45"/>
+      <c r="N125" s="45"/>
     </row>
     <row r="126" spans="1:14">
       <c r="A126" s="5"/>
       <c r="B126" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C126" s="35" t="s">
+      <c r="C126" s="30" t="s">
         <v>70</v>
       </c>
       <c r="D126" s="4"/>
@@ -12966,10 +12338,10 @@
         <v>46291</v>
       </c>
       <c r="H128" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I128" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J128" s="5" t="s">
         <v>71</v>
@@ -13008,10 +12380,10 @@
         <v>46291</v>
       </c>
       <c r="H129" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I129" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J129" s="5" t="s">
         <v>73</v>
@@ -13048,10 +12420,10 @@
         <v>46291</v>
       </c>
       <c r="H130" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I130" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J130" s="5" t="s">
         <v>75</v>
@@ -13088,10 +12460,10 @@
         <v>46291</v>
       </c>
       <c r="H131" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I131" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J131" s="5" t="s">
         <v>77</v>
@@ -13126,10 +12498,10 @@
         <v>46291</v>
       </c>
       <c r="H132" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I132" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J132" s="5" t="s">
         <v>79</v>
@@ -13164,10 +12536,10 @@
         <v>46291</v>
       </c>
       <c r="H133" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I133" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J133" s="5" t="s">
         <v>83</v>
@@ -13182,27 +12554,27 @@
       </c>
     </row>
     <row r="134" spans="1:14">
-      <c r="A134" s="17"/>
-      <c r="B134" s="17"/>
-      <c r="C134" s="17"/>
-      <c r="D134" s="17"/>
-      <c r="E134" s="17"/>
-      <c r="F134" s="17"/>
-      <c r="G134" s="17"/>
-      <c r="H134" s="17"/>
-      <c r="I134" s="17"/>
-      <c r="J134" s="17"/>
-      <c r="K134" s="17"/>
-      <c r="L134" s="17"/>
-      <c r="M134" s="17"/>
-      <c r="N134" s="17"/>
+      <c r="A134" s="45"/>
+      <c r="B134" s="45"/>
+      <c r="C134" s="45"/>
+      <c r="D134" s="45"/>
+      <c r="E134" s="45"/>
+      <c r="F134" s="45"/>
+      <c r="G134" s="45"/>
+      <c r="H134" s="45"/>
+      <c r="I134" s="45"/>
+      <c r="J134" s="45"/>
+      <c r="K134" s="45"/>
+      <c r="L134" s="45"/>
+      <c r="M134" s="45"/>
+      <c r="N134" s="45"/>
     </row>
     <row r="135" spans="1:14">
       <c r="A135" s="5"/>
       <c r="B135" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C135" s="35" t="s">
+      <c r="C135" s="30" t="s">
         <v>84</v>
       </c>
       <c r="D135" s="4"/>
@@ -13282,10 +12654,10 @@
         <v>46291</v>
       </c>
       <c r="H137" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I137" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J137" s="5" t="s">
         <v>256</v>
@@ -13324,10 +12696,10 @@
         <v>46291</v>
       </c>
       <c r="H138" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I138" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J138" s="5" t="s">
         <v>254</v>
@@ -13362,10 +12734,10 @@
         <v>46291</v>
       </c>
       <c r="H139" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I139" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J139" s="5" t="s">
         <v>303</v>
@@ -13402,10 +12774,10 @@
         <v>46291</v>
       </c>
       <c r="H140" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I140" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J140" s="5" t="s">
         <v>257</v>
@@ -13442,10 +12814,10 @@
         <v>46291</v>
       </c>
       <c r="H141" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I141" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J141" s="5" t="s">
         <v>255</v>
@@ -13480,10 +12852,10 @@
         <v>46291</v>
       </c>
       <c r="H142" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I142" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J142" s="5" t="s">
         <v>304</v>
@@ -13502,7 +12874,7 @@
       <c r="B144" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C144" s="35" t="s">
+      <c r="C144" s="30" t="s">
         <v>84</v>
       </c>
       <c r="D144" s="4"/>
@@ -13580,10 +12952,10 @@
         <v>46291</v>
       </c>
       <c r="H146" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I146" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J146" s="5" t="s">
         <v>85</v>
@@ -13622,10 +12994,10 @@
         <v>46291</v>
       </c>
       <c r="H147" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I147" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J147" s="5" t="s">
         <v>87</v>
@@ -13660,10 +13032,10 @@
         <v>46291</v>
       </c>
       <c r="H148" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I148" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J148" s="5" t="s">
         <v>89</v>
@@ -13700,10 +13072,10 @@
         <v>46291</v>
       </c>
       <c r="H149" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I149" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J149" s="5" t="s">
         <v>91</v>
@@ -13740,10 +13112,10 @@
         <v>46291</v>
       </c>
       <c r="H150" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I150" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J150" s="5" t="s">
         <v>93</v>
@@ -13778,10 +13150,10 @@
         <v>46291</v>
       </c>
       <c r="H151" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I151" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J151" s="5" t="s">
         <v>95</v>
@@ -13796,27 +13168,27 @@
       </c>
     </row>
     <row r="152" spans="1:14">
-      <c r="A152" s="17"/>
-      <c r="B152" s="17"/>
-      <c r="C152" s="17"/>
-      <c r="D152" s="17"/>
-      <c r="E152" s="17"/>
-      <c r="F152" s="17"/>
-      <c r="G152" s="17"/>
-      <c r="H152" s="17"/>
-      <c r="I152" s="17"/>
-      <c r="J152" s="17"/>
-      <c r="K152" s="17"/>
-      <c r="L152" s="17"/>
-      <c r="M152" s="17"/>
-      <c r="N152" s="17"/>
+      <c r="A152" s="45"/>
+      <c r="B152" s="45"/>
+      <c r="C152" s="45"/>
+      <c r="D152" s="45"/>
+      <c r="E152" s="45"/>
+      <c r="F152" s="45"/>
+      <c r="G152" s="45"/>
+      <c r="H152" s="45"/>
+      <c r="I152" s="45"/>
+      <c r="J152" s="45"/>
+      <c r="K152" s="45"/>
+      <c r="L152" s="45"/>
+      <c r="M152" s="45"/>
+      <c r="N152" s="45"/>
     </row>
     <row r="153" spans="1:14">
       <c r="A153" s="5"/>
       <c r="B153" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C153" s="35" t="s">
+      <c r="C153" s="30" t="s">
         <v>144</v>
       </c>
       <c r="D153" s="4"/>
@@ -13896,10 +13268,10 @@
         <v>46291</v>
       </c>
       <c r="H155" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I155" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J155" s="5" t="s">
         <v>306</v>
@@ -13940,10 +13312,10 @@
         <v>46291</v>
       </c>
       <c r="H156" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I156" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J156" s="5" t="s">
         <v>307</v>
@@ -13980,10 +13352,10 @@
         <v>46291</v>
       </c>
       <c r="H157" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I157" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J157" s="5" t="s">
         <v>308</v>
@@ -14020,10 +13392,10 @@
         <v>46291</v>
       </c>
       <c r="H158" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I158" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J158" s="5" t="s">
         <v>309</v>
@@ -14058,10 +13430,10 @@
         <v>46291</v>
       </c>
       <c r="H159" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I159" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J159" s="5" t="s">
         <v>310</v>
@@ -14096,10 +13468,10 @@
         <v>46291</v>
       </c>
       <c r="H160" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I160" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J160" s="5" t="s">
         <v>230</v>
@@ -14114,27 +13486,27 @@
       </c>
     </row>
     <row r="161" spans="1:14">
-      <c r="A161" s="17"/>
-      <c r="B161" s="17"/>
-      <c r="C161" s="17"/>
-      <c r="D161" s="17"/>
-      <c r="E161" s="17"/>
-      <c r="F161" s="17"/>
-      <c r="G161" s="17"/>
-      <c r="H161" s="17"/>
-      <c r="I161" s="17"/>
-      <c r="J161" s="17"/>
-      <c r="K161" s="17"/>
-      <c r="L161" s="17"/>
-      <c r="M161" s="17"/>
-      <c r="N161" s="17"/>
+      <c r="A161" s="45"/>
+      <c r="B161" s="45"/>
+      <c r="C161" s="45"/>
+      <c r="D161" s="45"/>
+      <c r="E161" s="45"/>
+      <c r="F161" s="45"/>
+      <c r="G161" s="45"/>
+      <c r="H161" s="45"/>
+      <c r="I161" s="45"/>
+      <c r="J161" s="45"/>
+      <c r="K161" s="45"/>
+      <c r="L161" s="45"/>
+      <c r="M161" s="45"/>
+      <c r="N161" s="45"/>
     </row>
     <row r="162" spans="1:14">
       <c r="A162" s="5"/>
       <c r="B162" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C162" s="35" t="s">
+      <c r="C162" s="30" t="s">
         <v>144</v>
       </c>
       <c r="D162" s="4"/>
@@ -14214,10 +13586,10 @@
         <v>46291</v>
       </c>
       <c r="H164" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I164" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J164" s="5" t="s">
         <v>145</v>
@@ -14258,10 +13630,10 @@
         <v>46291</v>
       </c>
       <c r="H165" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I165" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J165" s="5" t="s">
         <v>137</v>
@@ -14298,10 +13670,10 @@
         <v>46291</v>
       </c>
       <c r="H166" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I166" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J166" s="5" t="s">
         <v>157</v>
@@ -14342,10 +13714,10 @@
         <v>46291</v>
       </c>
       <c r="H167" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I167" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J167" s="5" t="s">
         <v>159</v>
@@ -14380,10 +13752,10 @@
         <v>46291</v>
       </c>
       <c r="H168" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I168" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J168" s="5" t="s">
         <v>97</v>
@@ -14422,10 +13794,10 @@
         <v>46291</v>
       </c>
       <c r="H169" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I169" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J169" s="5" t="s">
         <v>99</v>
@@ -14444,7 +13816,7 @@
       <c r="B171" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C171" s="35" t="s">
+      <c r="C171" s="30" t="s">
         <v>152</v>
       </c>
       <c r="D171" s="4"/>
@@ -14526,10 +13898,10 @@
         <v>46291</v>
       </c>
       <c r="H173" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I173" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J173" s="5" t="s">
         <v>311</v>
@@ -14570,10 +13942,10 @@
         <v>46291</v>
       </c>
       <c r="H174" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I174" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J174" s="5" t="s">
         <v>312</v>
@@ -14592,7 +13964,7 @@
       <c r="B176" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C176" s="35" t="s">
+      <c r="C176" s="30" t="s">
         <v>152</v>
       </c>
       <c r="D176" s="4"/>
@@ -14674,10 +14046,10 @@
         <v>46291</v>
       </c>
       <c r="H178" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I178" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J178" s="5" t="s">
         <v>153</v>
@@ -14718,10 +14090,10 @@
         <v>46291</v>
       </c>
       <c r="H179" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I179" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J179" s="5" t="s">
         <v>22</v>
@@ -14740,7 +14112,7 @@
       <c r="B181" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C181" s="35" t="s">
+      <c r="C181" s="30" t="s">
         <v>100</v>
       </c>
       <c r="D181" s="4"/>
@@ -14820,10 +14192,10 @@
         <v>46291</v>
       </c>
       <c r="H183" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I183" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J183" s="5" t="s">
         <v>313</v>
@@ -14864,10 +14236,10 @@
         <v>46291</v>
       </c>
       <c r="H184" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I184" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J184" s="5" t="s">
         <v>157</v>
@@ -14902,10 +14274,10 @@
         <v>46291</v>
       </c>
       <c r="H185" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I185" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J185" s="5" t="s">
         <v>314</v>
@@ -14940,10 +14312,10 @@
         <v>46291</v>
       </c>
       <c r="H186" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I186" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J186" s="5" t="s">
         <v>27</v>
@@ -14980,10 +14352,10 @@
         <v>46291</v>
       </c>
       <c r="H187" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I187" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J187" s="5" t="s">
         <v>159</v>
@@ -14998,27 +14370,27 @@
       </c>
     </row>
     <row r="188" spans="1:14">
-      <c r="A188" s="17"/>
-      <c r="B188" s="17"/>
-      <c r="C188" s="17"/>
-      <c r="D188" s="17"/>
-      <c r="E188" s="17"/>
-      <c r="F188" s="17"/>
-      <c r="G188" s="17"/>
-      <c r="H188" s="17"/>
-      <c r="I188" s="17"/>
-      <c r="J188" s="17"/>
-      <c r="K188" s="17"/>
-      <c r="L188" s="17"/>
-      <c r="M188" s="17"/>
-      <c r="N188" s="17"/>
+      <c r="A188" s="45"/>
+      <c r="B188" s="45"/>
+      <c r="C188" s="45"/>
+      <c r="D188" s="45"/>
+      <c r="E188" s="45"/>
+      <c r="F188" s="45"/>
+      <c r="G188" s="45"/>
+      <c r="H188" s="45"/>
+      <c r="I188" s="45"/>
+      <c r="J188" s="45"/>
+      <c r="K188" s="45"/>
+      <c r="L188" s="45"/>
+      <c r="M188" s="45"/>
+      <c r="N188" s="45"/>
     </row>
     <row r="189" spans="1:14">
       <c r="A189" s="5"/>
       <c r="B189" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C189" s="35" t="s">
+      <c r="C189" s="30" t="s">
         <v>100</v>
       </c>
       <c r="D189" s="4"/>
@@ -15098,10 +14470,10 @@
         <v>46291</v>
       </c>
       <c r="H191" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I191" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J191" s="5" t="s">
         <v>101</v>
@@ -15140,10 +14512,10 @@
         <v>46291</v>
       </c>
       <c r="H192" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I192" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J192" s="5" t="s">
         <v>103</v>
@@ -15178,10 +14550,10 @@
         <v>46291</v>
       </c>
       <c r="H193" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I193" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J193" s="5" t="s">
         <v>105</v>
@@ -15218,10 +14590,10 @@
         <v>46291</v>
       </c>
       <c r="H194" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I194" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J194" s="5" t="s">
         <v>149</v>
@@ -15262,10 +14634,10 @@
         <v>46291</v>
       </c>
       <c r="H195" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I195" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J195" s="5" t="s">
         <v>151</v>
@@ -15280,27 +14652,27 @@
       </c>
     </row>
     <row r="196" spans="1:14">
-      <c r="A196" s="17"/>
-      <c r="B196" s="17"/>
-      <c r="C196" s="17"/>
-      <c r="D196" s="17"/>
-      <c r="E196" s="17"/>
-      <c r="F196" s="17"/>
-      <c r="G196" s="17"/>
-      <c r="H196" s="17"/>
-      <c r="I196" s="17"/>
-      <c r="J196" s="17"/>
-      <c r="K196" s="17"/>
-      <c r="L196" s="17"/>
-      <c r="M196" s="17"/>
-      <c r="N196" s="17"/>
+      <c r="A196" s="45"/>
+      <c r="B196" s="45"/>
+      <c r="C196" s="45"/>
+      <c r="D196" s="45"/>
+      <c r="E196" s="45"/>
+      <c r="F196" s="45"/>
+      <c r="G196" s="45"/>
+      <c r="H196" s="45"/>
+      <c r="I196" s="45"/>
+      <c r="J196" s="45"/>
+      <c r="K196" s="45"/>
+      <c r="L196" s="45"/>
+      <c r="M196" s="45"/>
+      <c r="N196" s="45"/>
     </row>
     <row r="197" spans="1:14">
       <c r="A197" s="5"/>
       <c r="B197" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C197" s="35" t="s">
+      <c r="C197" s="30" t="s">
         <v>106</v>
       </c>
       <c r="D197" s="4"/>
@@ -15380,10 +14752,10 @@
         <v>46291</v>
       </c>
       <c r="H199" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I199" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J199" s="5" t="s">
         <v>316</v>
@@ -15422,10 +14794,10 @@
         <v>46291</v>
       </c>
       <c r="H200" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I200" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J200" s="5" t="s">
         <v>317</v>
@@ -15460,10 +14832,10 @@
         <v>46291</v>
       </c>
       <c r="H201" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I201" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J201" s="5" t="s">
         <v>318</v>
@@ -15498,10 +14870,10 @@
         <v>46291</v>
       </c>
       <c r="H202" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I202" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J202" s="5" t="s">
         <v>319</v>
@@ -15538,10 +14910,10 @@
         <v>46291</v>
       </c>
       <c r="H203" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I203" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J203" s="5" t="s">
         <v>320</v>
@@ -15576,10 +14948,10 @@
         <v>46291</v>
       </c>
       <c r="H204" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I204" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J204" s="5" t="s">
         <v>321</v>
@@ -15598,7 +14970,7 @@
       <c r="B206" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C206" s="35" t="s">
+      <c r="C206" s="30" t="s">
         <v>106</v>
       </c>
       <c r="D206" s="4"/>
@@ -15678,10 +15050,10 @@
         <v>46291</v>
       </c>
       <c r="H208" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I208" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J208" s="5" t="s">
         <v>107</v>
@@ -15720,10 +15092,10 @@
         <v>46291</v>
       </c>
       <c r="H209" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I209" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J209" s="5" t="s">
         <v>109</v>
@@ -15758,10 +15130,10 @@
         <v>46291</v>
       </c>
       <c r="H210" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I210" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J210" s="5" t="s">
         <v>111</v>
@@ -15796,10 +15168,10 @@
         <v>46291</v>
       </c>
       <c r="H211" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I211" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J211" s="5" t="s">
         <v>113</v>
@@ -15836,10 +15208,10 @@
         <v>46291</v>
       </c>
       <c r="H212" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I212" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J212" s="5" t="s">
         <v>181</v>
@@ -15878,10 +15250,10 @@
         <v>46291</v>
       </c>
       <c r="H213" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I213" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J213" s="5" t="s">
         <v>183</v>
@@ -15896,27 +15268,27 @@
       </c>
     </row>
     <row r="214" spans="1:14">
-      <c r="A214" s="17"/>
-      <c r="B214" s="17"/>
-      <c r="C214" s="17"/>
-      <c r="D214" s="17"/>
-      <c r="E214" s="17"/>
-      <c r="F214" s="17"/>
-      <c r="G214" s="17"/>
-      <c r="H214" s="17"/>
-      <c r="I214" s="17"/>
-      <c r="J214" s="17"/>
-      <c r="K214" s="17"/>
-      <c r="L214" s="17"/>
-      <c r="M214" s="17"/>
-      <c r="N214" s="17"/>
+      <c r="A214" s="45"/>
+      <c r="B214" s="45"/>
+      <c r="C214" s="45"/>
+      <c r="D214" s="45"/>
+      <c r="E214" s="45"/>
+      <c r="F214" s="45"/>
+      <c r="G214" s="45"/>
+      <c r="H214" s="45"/>
+      <c r="I214" s="45"/>
+      <c r="J214" s="45"/>
+      <c r="K214" s="45"/>
+      <c r="L214" s="45"/>
+      <c r="M214" s="45"/>
+      <c r="N214" s="45"/>
     </row>
     <row r="215" spans="1:14">
       <c r="A215" s="5"/>
       <c r="B215" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C215" s="35" t="s">
+      <c r="C215" s="30" t="s">
         <v>176</v>
       </c>
       <c r="D215" s="4"/>
@@ -15998,10 +15370,10 @@
         <v>46291</v>
       </c>
       <c r="H217" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I217" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J217" s="5" t="s">
         <v>153</v>
@@ -16040,10 +15412,10 @@
         <v>46291</v>
       </c>
       <c r="H218" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I218" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J218" s="5" t="s">
         <v>22</v>
@@ -16080,10 +15452,10 @@
         <v>46291</v>
       </c>
       <c r="H219" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I219" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J219" s="5" t="s">
         <v>241</v>
@@ -16118,10 +15490,10 @@
         <v>46291</v>
       </c>
       <c r="H220" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I220" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J220" s="5" t="s">
         <v>246</v>
@@ -16156,10 +15528,10 @@
         <v>46291</v>
       </c>
       <c r="H221" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I221" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J221" s="5" t="s">
         <v>244</v>
@@ -16194,10 +15566,10 @@
         <v>46291</v>
       </c>
       <c r="H222" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I222" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J222" s="5" t="s">
         <v>20</v>
@@ -16212,27 +15584,27 @@
       </c>
     </row>
     <row r="223" spans="1:14">
-      <c r="A223" s="17"/>
-      <c r="B223" s="17"/>
-      <c r="C223" s="17"/>
-      <c r="D223" s="17"/>
-      <c r="E223" s="17"/>
-      <c r="F223" s="17"/>
-      <c r="G223" s="17"/>
-      <c r="H223" s="17"/>
-      <c r="I223" s="17"/>
-      <c r="J223" s="17"/>
-      <c r="K223" s="17"/>
-      <c r="L223" s="17"/>
-      <c r="M223" s="17"/>
-      <c r="N223" s="17"/>
+      <c r="A223" s="45"/>
+      <c r="B223" s="45"/>
+      <c r="C223" s="45"/>
+      <c r="D223" s="45"/>
+      <c r="E223" s="45"/>
+      <c r="F223" s="45"/>
+      <c r="G223" s="45"/>
+      <c r="H223" s="45"/>
+      <c r="I223" s="45"/>
+      <c r="J223" s="45"/>
+      <c r="K223" s="45"/>
+      <c r="L223" s="45"/>
+      <c r="M223" s="45"/>
+      <c r="N223" s="45"/>
     </row>
     <row r="224" spans="1:14">
       <c r="A224" s="5"/>
       <c r="B224" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C224" s="35" t="s">
+      <c r="C224" s="30" t="s">
         <v>176</v>
       </c>
       <c r="D224" s="4"/>
@@ -16314,10 +15686,10 @@
         <v>46291</v>
       </c>
       <c r="H226" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I226" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J226" s="5" t="s">
         <v>177</v>
@@ -16356,10 +15728,10 @@
         <v>46291</v>
       </c>
       <c r="H227" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I227" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J227" s="5" t="s">
         <v>179</v>
@@ -16396,10 +15768,10 @@
         <v>46291</v>
       </c>
       <c r="H228" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I228" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J228" s="5" t="s">
         <v>191</v>
@@ -16438,10 +15810,10 @@
         <v>46291</v>
       </c>
       <c r="H229" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I229" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J229" s="5" t="s">
         <v>163</v>
@@ -16476,10 +15848,10 @@
         <v>46291</v>
       </c>
       <c r="H230" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I230" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J230" s="5" t="s">
         <v>322</v>
@@ -16518,10 +15890,10 @@
         <v>46291</v>
       </c>
       <c r="H231" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I231" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J231" s="5" t="s">
         <v>115</v>
@@ -16536,27 +15908,27 @@
       </c>
     </row>
     <row r="232" spans="1:14">
-      <c r="A232" s="17"/>
-      <c r="B232" s="17"/>
-      <c r="C232" s="17"/>
-      <c r="D232" s="17"/>
-      <c r="E232" s="17"/>
-      <c r="F232" s="17"/>
-      <c r="G232" s="17"/>
-      <c r="H232" s="17"/>
-      <c r="I232" s="17"/>
-      <c r="J232" s="17"/>
-      <c r="K232" s="17"/>
-      <c r="L232" s="17"/>
-      <c r="M232" s="17"/>
-      <c r="N232" s="17"/>
+      <c r="A232" s="45"/>
+      <c r="B232" s="45"/>
+      <c r="C232" s="45"/>
+      <c r="D232" s="45"/>
+      <c r="E232" s="45"/>
+      <c r="F232" s="45"/>
+      <c r="G232" s="45"/>
+      <c r="H232" s="45"/>
+      <c r="I232" s="45"/>
+      <c r="J232" s="45"/>
+      <c r="K232" s="45"/>
+      <c r="L232" s="45"/>
+      <c r="M232" s="45"/>
+      <c r="N232" s="45"/>
     </row>
     <row r="233" spans="1:14">
       <c r="A233" s="5"/>
       <c r="B233" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C233" s="35" t="s">
+      <c r="C233" s="30" t="s">
         <v>196</v>
       </c>
       <c r="D233" s="4"/>
@@ -16638,10 +16010,10 @@
         <v>46291</v>
       </c>
       <c r="H235" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I235" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J235" s="5" t="s">
         <v>149</v>
@@ -16682,10 +16054,10 @@
         <v>46291</v>
       </c>
       <c r="H236" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I236" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J236" s="5" t="s">
         <v>151</v>
@@ -16720,10 +16092,10 @@
         <v>46291</v>
       </c>
       <c r="H237" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I237" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J237" s="5" t="s">
         <v>231</v>
@@ -16758,10 +16130,10 @@
         <v>46291</v>
       </c>
       <c r="H238" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I238" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J238" s="5" t="s">
         <v>235</v>
@@ -16796,10 +16168,10 @@
         <v>46291</v>
       </c>
       <c r="H239" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I239" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J239" s="5" t="s">
         <v>237</v>
@@ -16834,10 +16206,10 @@
         <v>46291</v>
       </c>
       <c r="H240" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I240" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J240" s="5" t="s">
         <v>233</v>
@@ -16852,27 +16224,27 @@
       </c>
     </row>
     <row r="241" spans="1:14">
-      <c r="A241" s="17"/>
-      <c r="B241" s="17"/>
-      <c r="C241" s="17"/>
-      <c r="D241" s="17"/>
-      <c r="E241" s="17"/>
-      <c r="F241" s="17"/>
-      <c r="G241" s="17"/>
-      <c r="H241" s="17"/>
-      <c r="I241" s="17"/>
-      <c r="J241" s="17"/>
-      <c r="K241" s="17"/>
-      <c r="L241" s="17"/>
-      <c r="M241" s="17"/>
-      <c r="N241" s="17"/>
+      <c r="A241" s="45"/>
+      <c r="B241" s="45"/>
+      <c r="C241" s="45"/>
+      <c r="D241" s="45"/>
+      <c r="E241" s="45"/>
+      <c r="F241" s="45"/>
+      <c r="G241" s="45"/>
+      <c r="H241" s="45"/>
+      <c r="I241" s="45"/>
+      <c r="J241" s="45"/>
+      <c r="K241" s="45"/>
+      <c r="L241" s="45"/>
+      <c r="M241" s="45"/>
+      <c r="N241" s="45"/>
     </row>
     <row r="242" spans="1:14">
       <c r="A242" s="5"/>
       <c r="B242" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C242" s="35" t="s">
+      <c r="C242" s="30" t="s">
         <v>196</v>
       </c>
       <c r="D242" s="4"/>
@@ -16954,10 +16326,10 @@
         <v>46291</v>
       </c>
       <c r="H244" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I244" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J244" s="5" t="s">
         <v>33</v>
@@ -16998,10 +16370,10 @@
         <v>46291</v>
       </c>
       <c r="H245" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I245" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J245" s="5" t="s">
         <v>39</v>
@@ -17036,10 +16408,10 @@
         <v>46291</v>
       </c>
       <c r="H246" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I246" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J246" s="5" t="s">
         <v>57</v>
@@ -17078,10 +16450,10 @@
         <v>46291</v>
       </c>
       <c r="H247" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I247" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J247" s="5" t="s">
         <v>60</v>
@@ -17116,10 +16488,10 @@
         <v>46291</v>
       </c>
       <c r="H248" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I248" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J248" s="5" t="s">
         <v>118</v>
@@ -17158,10 +16530,10 @@
         <v>46291</v>
       </c>
       <c r="H249" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I249" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J249" s="5" t="s">
         <v>120</v>
@@ -17176,26 +16548,26 @@
       </c>
     </row>
     <row r="250" spans="1:14">
-      <c r="B250" s="17"/>
-      <c r="C250" s="17"/>
-      <c r="D250" s="17"/>
-      <c r="E250" s="17"/>
-      <c r="F250" s="17"/>
-      <c r="G250" s="17"/>
-      <c r="H250" s="17"/>
-      <c r="I250" s="17"/>
-      <c r="J250" s="17"/>
-      <c r="K250" s="17"/>
-      <c r="L250" s="17"/>
-      <c r="M250" s="17"/>
-      <c r="N250" s="17"/>
+      <c r="B250" s="45"/>
+      <c r="C250" s="45"/>
+      <c r="D250" s="45"/>
+      <c r="E250" s="45"/>
+      <c r="F250" s="45"/>
+      <c r="G250" s="45"/>
+      <c r="H250" s="45"/>
+      <c r="I250" s="45"/>
+      <c r="J250" s="45"/>
+      <c r="K250" s="45"/>
+      <c r="L250" s="45"/>
+      <c r="M250" s="45"/>
+      <c r="N250" s="45"/>
     </row>
     <row r="251" spans="1:14">
       <c r="A251" s="5"/>
       <c r="B251" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C251" s="35" t="s">
+      <c r="C251" s="30" t="s">
         <v>212</v>
       </c>
       <c r="D251" s="4"/>
@@ -17277,10 +16649,10 @@
         <v>46291</v>
       </c>
       <c r="H253" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I253" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J253" s="5" t="s">
         <v>323</v>
@@ -17321,10 +16693,10 @@
         <v>46291</v>
       </c>
       <c r="H254" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I254" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J254" s="5" t="s">
         <v>324</v>
@@ -17340,26 +16712,26 @@
     </row>
     <row r="255" spans="1:14">
       <c r="A255" s="14"/>
-      <c r="B255" s="21"/>
-      <c r="C255" s="22"/>
-      <c r="D255" s="22"/>
-      <c r="E255" s="22"/>
-      <c r="F255" s="22"/>
-      <c r="G255" s="22"/>
-      <c r="H255" s="22"/>
-      <c r="I255" s="22"/>
-      <c r="J255" s="22"/>
-      <c r="K255" s="22"/>
-      <c r="L255" s="22"/>
-      <c r="M255" s="22"/>
-      <c r="N255" s="23"/>
+      <c r="B255" s="47"/>
+      <c r="C255" s="48"/>
+      <c r="D255" s="48"/>
+      <c r="E255" s="48"/>
+      <c r="F255" s="48"/>
+      <c r="G255" s="48"/>
+      <c r="H255" s="48"/>
+      <c r="I255" s="48"/>
+      <c r="J255" s="48"/>
+      <c r="K255" s="48"/>
+      <c r="L255" s="48"/>
+      <c r="M255" s="48"/>
+      <c r="N255" s="49"/>
     </row>
     <row r="256" spans="1:14">
       <c r="A256" s="5"/>
       <c r="B256" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C256" s="35" t="s">
+      <c r="C256" s="30" t="s">
         <v>212</v>
       </c>
       <c r="D256" s="4"/>
@@ -17441,10 +16813,10 @@
         <v>46291</v>
       </c>
       <c r="H258" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I258" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J258" s="5" t="s">
         <v>213</v>
@@ -17485,10 +16857,10 @@
         <v>46291</v>
       </c>
       <c r="H259" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I259" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J259" s="5" t="s">
         <v>203</v>
@@ -17507,7 +16879,7 @@
       <c r="B261" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C261" s="35" t="s">
+      <c r="C261" s="30" t="s">
         <v>142</v>
       </c>
       <c r="D261" s="4"/>
@@ -17589,10 +16961,10 @@
         <v>46291</v>
       </c>
       <c r="H263" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I263" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J263" s="5" t="s">
         <v>325</v>
@@ -17633,10 +17005,10 @@
         <v>46291</v>
       </c>
       <c r="H264" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I264" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J264" s="5" t="s">
         <v>326</v>
@@ -17671,10 +17043,10 @@
         <v>46291</v>
       </c>
       <c r="H265" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I265" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J265" s="5" t="s">
         <v>327</v>
@@ -17713,10 +17085,10 @@
         <v>46291</v>
       </c>
       <c r="H266" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I266" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J266" s="5" t="s">
         <v>328</v>
@@ -17735,7 +17107,7 @@
       <c r="B268" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C268" s="35" t="s">
+      <c r="C268" s="30" t="s">
         <v>142</v>
       </c>
       <c r="D268" s="4"/>
@@ -17817,10 +17189,10 @@
         <v>46291</v>
       </c>
       <c r="H270" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I270" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J270" s="5" t="s">
         <v>143</v>
@@ -17861,10 +17233,10 @@
         <v>46291</v>
       </c>
       <c r="H271" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I271" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J271" s="5" t="s">
         <v>161</v>
@@ -17899,10 +17271,10 @@
         <v>46291</v>
       </c>
       <c r="H272" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I272" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J272" s="5" t="s">
         <v>189</v>
@@ -17941,10 +17313,10 @@
         <v>46291</v>
       </c>
       <c r="H273" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I273" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J273" s="5" t="s">
         <v>199</v>
@@ -17966,7 +17338,7 @@
       <c r="B275" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C275" s="35" t="s">
+      <c r="C275" s="30" t="s">
         <v>121</v>
       </c>
       <c r="D275" s="4"/>
@@ -18046,10 +17418,10 @@
         <v>46291</v>
       </c>
       <c r="H277" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I277" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J277" s="5" t="s">
         <v>27</v>
@@ -18088,10 +17460,10 @@
         <v>46291</v>
       </c>
       <c r="H278" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I278" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J278" s="5" t="s">
         <v>329</v>
@@ -18126,10 +17498,10 @@
         <v>46291</v>
       </c>
       <c r="H279" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I279" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J279" s="5" t="s">
         <v>330</v>
@@ -18148,7 +17520,7 @@
       <c r="B281" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C281" s="35" t="s">
+      <c r="C281" s="30" t="s">
         <v>121</v>
       </c>
       <c r="D281" s="4"/>
@@ -18228,10 +17600,10 @@
         <v>46291</v>
       </c>
       <c r="H283" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I283" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J283" s="5" t="s">
         <v>122</v>
@@ -18270,10 +17642,10 @@
         <v>46291</v>
       </c>
       <c r="H284" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I284" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J284" s="5" t="s">
         <v>124</v>
@@ -18308,10 +17680,10 @@
         <v>46291</v>
       </c>
       <c r="H285" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I285" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J285" s="5" t="s">
         <v>126</v>
@@ -18330,7 +17702,7 @@
       <c r="B287" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C287" s="35" t="s">
+      <c r="C287" s="30" t="s">
         <v>214</v>
       </c>
       <c r="D287" s="4"/>
@@ -18412,10 +17784,10 @@
         <v>46291</v>
       </c>
       <c r="H289" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I289" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J289" s="5" t="s">
         <v>262</v>
@@ -18454,10 +17826,10 @@
         <v>46291</v>
       </c>
       <c r="H290" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I290" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J290" s="5" t="s">
         <v>260</v>
@@ -18492,10 +17864,10 @@
         <v>46291</v>
       </c>
       <c r="H291" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I291" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J291" s="5" t="s">
         <v>258</v>
@@ -18530,10 +17902,10 @@
         <v>46291</v>
       </c>
       <c r="H292" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I292" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J292" s="5" t="s">
         <v>259</v>
@@ -18568,10 +17940,10 @@
         <v>46291</v>
       </c>
       <c r="H293" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I293" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J293" s="5" t="s">
         <v>218</v>
@@ -18606,10 +17978,10 @@
         <v>46291</v>
       </c>
       <c r="H294" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I294" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J294" s="5" t="s">
         <v>261</v>
@@ -18624,27 +17996,27 @@
       </c>
     </row>
     <row r="295" spans="1:14">
-      <c r="A295" s="16"/>
-      <c r="B295" s="17"/>
-      <c r="C295" s="17"/>
-      <c r="D295" s="17"/>
-      <c r="E295" s="17"/>
-      <c r="F295" s="17"/>
-      <c r="G295" s="17"/>
-      <c r="H295" s="17"/>
-      <c r="I295" s="17"/>
-      <c r="J295" s="17"/>
-      <c r="K295" s="17"/>
-      <c r="L295" s="17"/>
-      <c r="M295" s="17"/>
-      <c r="N295" s="18"/>
+      <c r="A295" s="44"/>
+      <c r="B295" s="45"/>
+      <c r="C295" s="45"/>
+      <c r="D295" s="45"/>
+      <c r="E295" s="45"/>
+      <c r="F295" s="45"/>
+      <c r="G295" s="45"/>
+      <c r="H295" s="45"/>
+      <c r="I295" s="45"/>
+      <c r="J295" s="45"/>
+      <c r="K295" s="45"/>
+      <c r="L295" s="45"/>
+      <c r="M295" s="45"/>
+      <c r="N295" s="46"/>
     </row>
     <row r="296" spans="1:14">
       <c r="A296" s="5"/>
       <c r="B296" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C296" s="35" t="s">
+      <c r="C296" s="30" t="s">
         <v>214</v>
       </c>
       <c r="D296" s="4"/>
@@ -18726,10 +18098,10 @@
         <v>46291</v>
       </c>
       <c r="H298" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I298" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J298" s="5" t="s">
         <v>262</v>
@@ -18768,10 +18140,10 @@
         <v>46291</v>
       </c>
       <c r="H299" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I299" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J299" s="5" t="s">
         <v>260</v>
@@ -18806,10 +18178,10 @@
         <v>46291</v>
       </c>
       <c r="H300" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I300" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J300" s="5" t="s">
         <v>258</v>
@@ -18844,10 +18216,10 @@
         <v>46291</v>
       </c>
       <c r="H301" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I301" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J301" s="5" t="s">
         <v>259</v>
@@ -18882,10 +18254,10 @@
         <v>46291</v>
       </c>
       <c r="H302" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I302" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J302" s="5" t="s">
         <v>218</v>
@@ -18920,10 +18292,10 @@
         <v>46291</v>
       </c>
       <c r="H303" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I303" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J303" s="5" t="s">
         <v>261</v>
@@ -18940,7 +18312,7 @@
       <c r="B305" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C305" s="35" t="s">
+      <c r="C305" s="30" t="s">
         <v>214</v>
       </c>
       <c r="D305" s="4"/>
@@ -19022,10 +18394,10 @@
         <v>46291</v>
       </c>
       <c r="H307" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I307" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J307" s="5" t="s">
         <v>231</v>
@@ -19064,10 +18436,10 @@
         <v>46291</v>
       </c>
       <c r="H308" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I308" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J308" s="5" t="s">
         <v>233</v>
@@ -19100,10 +18472,10 @@
         <v>46291</v>
       </c>
       <c r="H309" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I309" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J309" s="5" t="s">
         <v>235</v>
@@ -19136,10 +18508,10 @@
         <v>46291</v>
       </c>
       <c r="H310" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I310" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J310" s="5" t="s">
         <v>237</v>
@@ -19172,10 +18544,10 @@
         <v>46291</v>
       </c>
       <c r="H311" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I311" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J311" s="5" t="s">
         <v>218</v>
@@ -19208,10 +18580,10 @@
         <v>46291</v>
       </c>
       <c r="H312" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I312" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J312" s="5" t="s">
         <v>239</v>
@@ -19228,7 +18600,7 @@
       <c r="B314" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C314" s="35" t="s">
+      <c r="C314" s="30" t="s">
         <v>200</v>
       </c>
       <c r="D314" s="4"/>
@@ -19310,10 +18682,10 @@
         <v>46291</v>
       </c>
       <c r="H316" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I316" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J316" s="5" t="s">
         <v>331</v>
@@ -19354,10 +18726,10 @@
         <v>46291</v>
       </c>
       <c r="H317" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I317" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J317" s="5" t="s">
         <v>332</v>
@@ -19374,7 +18746,7 @@
       <c r="B319" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C319" s="35" t="s">
+      <c r="C319" s="30" t="s">
         <v>200</v>
       </c>
       <c r="D319" s="4"/>
@@ -19456,10 +18828,10 @@
         <v>46291</v>
       </c>
       <c r="H321" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I321" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J321" s="5" t="s">
         <v>201</v>
@@ -19500,10 +18872,10 @@
         <v>46291</v>
       </c>
       <c r="H322" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I322" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J322" s="5" t="s">
         <v>193</v>
@@ -19520,7 +18892,7 @@
       <c r="B324" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C324" s="35" t="s">
+      <c r="C324" s="30" t="s">
         <v>333</v>
       </c>
       <c r="D324" s="4"/>
@@ -19602,10 +18974,10 @@
         <v>46291</v>
       </c>
       <c r="H326" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I326" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J326" s="5" t="s">
         <v>334</v>
@@ -19646,10 +19018,10 @@
         <v>46291</v>
       </c>
       <c r="H327" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I327" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J327" s="5" t="s">
         <v>161</v>
@@ -19682,10 +19054,10 @@
         <v>46291</v>
       </c>
       <c r="H328" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I328" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J328" s="5" t="s">
         <v>335</v>
@@ -19718,10 +19090,10 @@
         <v>46291</v>
       </c>
       <c r="H329" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I329" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J329" s="5" t="s">
         <v>336</v>
@@ -19754,10 +19126,10 @@
         <v>46291</v>
       </c>
       <c r="H330" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I330" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J330" s="5" t="s">
         <v>337</v>
@@ -19774,7 +19146,7 @@
       <c r="B332" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C332" s="35" t="s">
+      <c r="C332" s="30" t="s">
         <v>333</v>
       </c>
       <c r="D332" s="4"/>
@@ -19856,10 +19228,10 @@
         <v>46291</v>
       </c>
       <c r="H334" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I334" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J334" s="5" t="s">
         <v>249</v>
@@ -19900,10 +19272,10 @@
         <v>46291</v>
       </c>
       <c r="H335" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I335" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J335" s="5" t="s">
         <v>252</v>
@@ -19936,10 +19308,10 @@
         <v>46291</v>
       </c>
       <c r="H336" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I336" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J336" s="5" t="s">
         <v>251</v>
@@ -19972,10 +19344,10 @@
         <v>46291</v>
       </c>
       <c r="H337" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I337" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J337" s="5" t="s">
         <v>250</v>
@@ -20008,10 +19380,10 @@
         <v>46291</v>
       </c>
       <c r="H338" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I338" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J338" s="5" t="s">
         <v>253</v>
@@ -20028,7 +19400,7 @@
       <c r="B340" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C340" s="35" t="s">
+      <c r="C340" s="30" t="s">
         <v>333</v>
       </c>
       <c r="D340" s="4"/>
@@ -20110,10 +19482,10 @@
         <v>46291</v>
       </c>
       <c r="H342" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I342" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J342" s="5" t="s">
         <v>222</v>
@@ -20154,10 +19526,10 @@
         <v>46291</v>
       </c>
       <c r="H343" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I343" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J343" s="5" t="s">
         <v>226</v>
@@ -20192,10 +19564,10 @@
         <v>46291</v>
       </c>
       <c r="H344" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I344" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J344" s="5" t="s">
         <v>228</v>
@@ -20230,10 +19602,10 @@
         <v>46291</v>
       </c>
       <c r="H345" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I345" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J345" s="5" t="s">
         <v>224</v>
@@ -20268,10 +19640,10 @@
         <v>46291</v>
       </c>
       <c r="H346" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I346" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J346" s="5" t="s">
         <v>230</v>
@@ -20290,7 +19662,7 @@
       <c r="B348" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C348" s="35" t="s">
+      <c r="C348" s="30" t="s">
         <v>208</v>
       </c>
       <c r="D348" s="4"/>
@@ -20372,10 +19744,10 @@
         <v>46291</v>
       </c>
       <c r="H350" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I350" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J350" s="5" t="s">
         <v>338</v>
@@ -20416,10 +19788,10 @@
         <v>46291</v>
       </c>
       <c r="H351" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I351" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J351" s="5" t="s">
         <v>339</v>
@@ -20456,10 +19828,10 @@
         <v>46291</v>
       </c>
       <c r="H352" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I352" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J352" s="5" t="s">
         <v>340</v>
@@ -20500,10 +19872,10 @@
         <v>46291</v>
       </c>
       <c r="H353" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I353" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J353" s="5" t="s">
         <v>341</v>
@@ -20522,7 +19894,7 @@
       <c r="B355" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C355" s="35" t="s">
+      <c r="C355" s="30" t="s">
         <v>208</v>
       </c>
       <c r="D355" s="4"/>
@@ -20604,10 +19976,10 @@
         <v>46291</v>
       </c>
       <c r="H357" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I357" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J357" s="5" t="s">
         <v>209</v>
@@ -20648,10 +20020,10 @@
         <v>46291</v>
       </c>
       <c r="H358" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I358" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J358" s="5" t="s">
         <v>211</v>
@@ -20688,10 +20060,10 @@
         <v>46291</v>
       </c>
       <c r="H359" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I359" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J359" s="5" t="s">
         <v>205</v>
@@ -20732,10 +20104,10 @@
         <v>46291</v>
       </c>
       <c r="H360" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I360" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J360" s="5" t="s">
         <v>207</v>
@@ -20754,7 +20126,7 @@
       <c r="B362" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C362" s="35" t="s">
+      <c r="C362" s="30" t="s">
         <v>240</v>
       </c>
       <c r="D362" s="4"/>
@@ -20836,10 +20208,10 @@
         <v>46291</v>
       </c>
       <c r="H364" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I364" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J364" s="5" t="s">
         <v>143</v>
@@ -20878,10 +20250,10 @@
         <v>46291</v>
       </c>
       <c r="H365" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I365" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J365" s="5" t="s">
         <v>342</v>
@@ -20916,10 +20288,10 @@
         <v>46291</v>
       </c>
       <c r="H366" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I366" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J366" s="5" t="s">
         <v>343</v>
@@ -20954,10 +20326,10 @@
         <v>46291</v>
       </c>
       <c r="H367" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I367" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J367" s="5" t="s">
         <v>344</v>
@@ -20992,10 +20364,10 @@
         <v>46291</v>
       </c>
       <c r="H368" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I368" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J368" s="5" t="s">
         <v>220</v>
@@ -21014,7 +20386,7 @@
       <c r="B370" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C370" s="35" t="s">
+      <c r="C370" s="30" t="s">
         <v>240</v>
       </c>
       <c r="D370" s="4"/>
@@ -21096,10 +20468,10 @@
         <v>46291</v>
       </c>
       <c r="H372" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I372" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J372" s="5" t="s">
         <v>254</v>
@@ -21138,10 +20510,10 @@
         <v>46291</v>
       </c>
       <c r="H373" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I373" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J373" s="5" t="s">
         <v>257</v>
@@ -21176,10 +20548,10 @@
         <v>46291</v>
       </c>
       <c r="H374" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I374" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J374" s="5" t="s">
         <v>255</v>
@@ -21214,10 +20586,10 @@
         <v>46291</v>
       </c>
       <c r="H375" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I375" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J375" s="5" t="s">
         <v>256</v>
@@ -21252,10 +20624,10 @@
         <v>46291</v>
       </c>
       <c r="H376" s="9">
-        <v>0.572916666666667</v>
+        <v>0.57291666666666696</v>
       </c>
       <c r="I376" s="9">
-        <v>0.809027777777778</v>
+        <v>0.80902777777777801</v>
       </c>
       <c r="J376" s="5" t="s">
         <v>220</v>
@@ -21274,7 +20646,7 @@
       <c r="B378" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C378" s="35" t="s">
+      <c r="C378" s="30" t="s">
         <v>240</v>
       </c>
       <c r="D378" s="4"/>
@@ -21356,10 +20728,10 @@
         <v>46291</v>
       </c>
       <c r="H380" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I380" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J380" s="5" t="s">
         <v>241</v>
@@ -21398,10 +20770,10 @@
         <v>46291</v>
       </c>
       <c r="H381" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I381" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J381" s="5" t="s">
         <v>20</v>
@@ -21436,10 +20808,10 @@
         <v>46291</v>
       </c>
       <c r="H382" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I382" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J382" s="5" t="s">
         <v>244</v>
@@ -21474,10 +20846,10 @@
         <v>46291</v>
       </c>
       <c r="H383" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I383" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J383" s="5" t="s">
         <v>246</v>
@@ -21512,10 +20884,10 @@
         <v>46291</v>
       </c>
       <c r="H384" s="9">
-        <v>0.815972222222222</v>
+        <v>0.81597222222222199</v>
       </c>
       <c r="I384" s="9">
-        <v>0.354166666666667</v>
+        <v>0.35416666666666702</v>
       </c>
       <c r="J384" s="5" t="s">
         <v>220</v>
@@ -21531,59 +20903,57 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A232:N232"/>
+    <mergeCell ref="A241:N241"/>
+    <mergeCell ref="B250:N250"/>
+    <mergeCell ref="B255:N255"/>
+    <mergeCell ref="A295:N295"/>
+    <mergeCell ref="A161:N161"/>
+    <mergeCell ref="A188:N188"/>
+    <mergeCell ref="A196:N196"/>
+    <mergeCell ref="A214:N214"/>
+    <mergeCell ref="A223:N223"/>
+    <mergeCell ref="A98:N98"/>
+    <mergeCell ref="A116:N116"/>
+    <mergeCell ref="A125:N125"/>
+    <mergeCell ref="A134:N134"/>
+    <mergeCell ref="A152:N152"/>
+    <mergeCell ref="A44:N44"/>
+    <mergeCell ref="A53:N53"/>
+    <mergeCell ref="A62:N62"/>
+    <mergeCell ref="A71:N71"/>
+    <mergeCell ref="A80:N80"/>
     <mergeCell ref="A7:N7"/>
     <mergeCell ref="A12:N12"/>
     <mergeCell ref="A19:N19"/>
     <mergeCell ref="A26:N26"/>
     <mergeCell ref="A35:N35"/>
-    <mergeCell ref="A44:N44"/>
-    <mergeCell ref="A53:N53"/>
-    <mergeCell ref="A62:N62"/>
-    <mergeCell ref="A71:N71"/>
-    <mergeCell ref="A80:N80"/>
-    <mergeCell ref="A98:N98"/>
-    <mergeCell ref="A116:N116"/>
-    <mergeCell ref="A125:N125"/>
-    <mergeCell ref="A134:N134"/>
-    <mergeCell ref="A152:N152"/>
-    <mergeCell ref="A161:N161"/>
-    <mergeCell ref="A188:N188"/>
-    <mergeCell ref="A196:N196"/>
-    <mergeCell ref="A214:N214"/>
-    <mergeCell ref="A223:N223"/>
-    <mergeCell ref="A232:N232"/>
-    <mergeCell ref="A241:N241"/>
-    <mergeCell ref="B250:N250"/>
-    <mergeCell ref="B255:N255"/>
-    <mergeCell ref="A295:N295"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A2:N95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="7.42857142857143" customWidth="1"/>
-    <col min="2" max="2" width="6.71428571428571" customWidth="1"/>
-    <col min="3" max="3" width="30.2857142857143" customWidth="1"/>
-    <col min="4" max="4" width="6.57142857142857" customWidth="1"/>
-    <col min="5" max="5" width="6.71428571428571" customWidth="1"/>
-    <col min="6" max="6" width="5.57142857142857" customWidth="1"/>
-    <col min="7" max="7" width="10" customWidth="1"/>
-    <col min="8" max="8" width="8.14285714285714" customWidth="1"/>
-    <col min="9" max="9" width="9.14285714285714" customWidth="1"/>
-    <col min="10" max="10" width="16.4285714285714" customWidth="1"/>
+    <col min="1" max="1" width="7.42578125" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" customWidth="1"/>
+    <col min="3" max="3" width="30.28515625" customWidth="1"/>
+    <col min="4" max="4" width="6.5703125" customWidth="1"/>
+    <col min="5" max="5" width="6.7109375" customWidth="1"/>
+    <col min="6" max="6" width="5.5703125" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.140625" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" customWidth="1"/>
+    <col min="10" max="10" width="16.42578125" customWidth="1"/>
     <col min="11" max="12" width="9" customWidth="1"/>
-    <col min="13" max="13" width="10.1428571428571" customWidth="1"/>
-    <col min="14" max="14" width="9.71428571428571" customWidth="1"/>
+    <col min="13" max="13" width="10.140625" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="26.25" spans="1:14">
+    <row r="2" spans="1:14" ht="26.25">
       <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
@@ -21633,7 +21003,7 @@
       </c>
       <c r="N3" s="5"/>
     </row>
-    <row r="4" ht="26.25" spans="1:14">
+    <row r="4" spans="1:14" ht="26.25">
       <c r="A4" s="5"/>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
@@ -21676,7 +21046,7 @@
         <v>46291</v>
       </c>
       <c r="H5" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I5" s="12" t="s">
         <v>279</v>
@@ -21716,7 +21086,7 @@
         <v>46291</v>
       </c>
       <c r="H6" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>279</v>
@@ -21760,7 +21130,7 @@
         <v>46291</v>
       </c>
       <c r="H7" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I7" s="12" t="s">
         <v>281</v>
@@ -21800,7 +21170,7 @@
         <v>46291</v>
       </c>
       <c r="H8" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I8" s="12" t="s">
         <v>281</v>
@@ -21838,10 +21208,10 @@
         <v>46291</v>
       </c>
       <c r="H9" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I9" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>218</v>
@@ -21874,10 +21244,10 @@
         <v>46291</v>
       </c>
       <c r="H10" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I10" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>220</v>
@@ -21910,10 +21280,10 @@
         <v>46291</v>
       </c>
       <c r="H11" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I11" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>306</v>
@@ -21954,10 +21324,10 @@
         <v>46291</v>
       </c>
       <c r="H12" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I12" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>308</v>
@@ -21992,10 +21362,10 @@
         <v>46291</v>
       </c>
       <c r="H13" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I13" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>230</v>
@@ -22032,10 +21402,10 @@
         <v>46291</v>
       </c>
       <c r="H14" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I14" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J14" s="5" t="s">
         <v>307</v>
@@ -22072,10 +21442,10 @@
         <v>46291</v>
       </c>
       <c r="H15" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I15" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>309</v>
@@ -22110,10 +21480,10 @@
         <v>46291</v>
       </c>
       <c r="H16" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I16" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>310</v>
@@ -22150,10 +21520,10 @@
         <v>46291</v>
       </c>
       <c r="H17" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I17" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J17" s="5" t="s">
         <v>249</v>
@@ -22188,10 +21558,10 @@
         <v>46291</v>
       </c>
       <c r="H18" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I18" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>250</v>
@@ -22230,10 +21600,10 @@
         <v>46291</v>
       </c>
       <c r="H19" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I19" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>251</v>
@@ -22270,10 +21640,10 @@
         <v>46291</v>
       </c>
       <c r="H20" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I20" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>252</v>
@@ -22308,10 +21678,10 @@
         <v>46291</v>
       </c>
       <c r="H21" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I21" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>253</v>
@@ -22346,10 +21716,10 @@
         <v>46291</v>
       </c>
       <c r="H22" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I22" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>297</v>
@@ -22384,10 +21754,10 @@
         <v>46291</v>
       </c>
       <c r="H23" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I23" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>254</v>
@@ -22424,10 +21794,10 @@
         <v>46291</v>
       </c>
       <c r="H24" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I24" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>255</v>
@@ -22462,10 +21832,10 @@
         <v>46291</v>
       </c>
       <c r="H25" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I25" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>256</v>
@@ -22506,10 +21876,10 @@
         <v>46291</v>
       </c>
       <c r="H26" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I26" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>257</v>
@@ -22544,10 +21914,10 @@
         <v>46291</v>
       </c>
       <c r="H27" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I27" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J27" s="5" t="s">
         <v>303</v>
@@ -22582,10 +21952,10 @@
         <v>46291</v>
       </c>
       <c r="H28" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I28" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J28" s="5" t="s">
         <v>304</v>
@@ -22622,10 +21992,10 @@
         <v>46291</v>
       </c>
       <c r="H29" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I29" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J29" s="5" t="s">
         <v>143</v>
@@ -22664,10 +22034,10 @@
         <v>46291</v>
       </c>
       <c r="H30" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I30" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>342</v>
@@ -22702,10 +22072,10 @@
         <v>46291</v>
       </c>
       <c r="H31" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I31" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>343</v>
@@ -22740,10 +22110,10 @@
         <v>46291</v>
       </c>
       <c r="H32" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I32" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J32" s="5" t="s">
         <v>344</v>
@@ -22780,10 +22150,10 @@
         <v>46291</v>
       </c>
       <c r="H33" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I33" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J33" s="5" t="s">
         <v>311</v>
@@ -22824,10 +22194,10 @@
         <v>46291</v>
       </c>
       <c r="H34" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I34" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J34" s="5" t="s">
         <v>312</v>
@@ -22864,10 +22234,10 @@
         <v>46291</v>
       </c>
       <c r="H35" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I35" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J35" s="5" t="s">
         <v>331</v>
@@ -22908,10 +22278,10 @@
         <v>46291</v>
       </c>
       <c r="H36" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I36" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J36" s="5" t="s">
         <v>332</v>
@@ -22948,10 +22318,10 @@
         <v>46291</v>
       </c>
       <c r="H37" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I37" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J37" s="5" t="s">
         <v>338</v>
@@ -22992,10 +22362,10 @@
         <v>46291</v>
       </c>
       <c r="H38" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I38" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J38" s="5" t="s">
         <v>339</v>
@@ -23032,10 +22402,10 @@
         <v>46291</v>
       </c>
       <c r="H39" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I39" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J39" s="5" t="s">
         <v>334</v>
@@ -23074,10 +22444,10 @@
         <v>46291</v>
       </c>
       <c r="H40" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I40" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J40" s="5" t="s">
         <v>258</v>
@@ -23112,10 +22482,10 @@
         <v>46291</v>
       </c>
       <c r="H41" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I41" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J41" s="5" t="s">
         <v>259</v>
@@ -23150,10 +22520,10 @@
         <v>46291</v>
       </c>
       <c r="H42" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I42" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J42" s="5" t="s">
         <v>260</v>
@@ -23188,10 +22558,10 @@
         <v>46291</v>
       </c>
       <c r="H43" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I43" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J43" s="5" t="s">
         <v>261</v>
@@ -23228,10 +22598,10 @@
         <v>46291</v>
       </c>
       <c r="H44" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I44" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J44" s="5" t="s">
         <v>149</v>
@@ -23270,10 +22640,10 @@
         <v>46291</v>
       </c>
       <c r="H45" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I45" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J45" s="5" t="s">
         <v>231</v>
@@ -23308,10 +22678,10 @@
         <v>46291</v>
       </c>
       <c r="H46" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I46" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J46" s="5" t="s">
         <v>233</v>
@@ -23346,10 +22716,10 @@
         <v>46291</v>
       </c>
       <c r="H47" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I47" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J47" s="5" t="s">
         <v>336</v>
@@ -23386,10 +22756,10 @@
         <v>46291</v>
       </c>
       <c r="H48" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I48" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J48" s="5" t="s">
         <v>151</v>
@@ -23424,10 +22794,10 @@
         <v>46291</v>
       </c>
       <c r="H49" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I49" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J49" s="5" t="s">
         <v>235</v>
@@ -23462,10 +22832,10 @@
         <v>46291</v>
       </c>
       <c r="H50" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I50" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J50" s="5" t="s">
         <v>237</v>
@@ -23502,10 +22872,10 @@
         <v>46291</v>
       </c>
       <c r="H51" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I51" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J51" s="5" t="s">
         <v>153</v>
@@ -23546,10 +22916,10 @@
         <v>46291</v>
       </c>
       <c r="H52" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I52" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J52" s="5" t="s">
         <v>241</v>
@@ -23584,10 +22954,10 @@
         <v>46291</v>
       </c>
       <c r="H53" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I53" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J53" s="5" t="s">
         <v>20</v>
@@ -23622,10 +22992,10 @@
         <v>46291</v>
       </c>
       <c r="H54" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I54" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J54" s="5" t="s">
         <v>22</v>
@@ -23660,10 +23030,10 @@
         <v>46291</v>
       </c>
       <c r="H55" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I55" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J55" s="5" t="s">
         <v>244</v>
@@ -23698,10 +23068,10 @@
         <v>46291</v>
       </c>
       <c r="H56" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I56" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J56" s="5" t="s">
         <v>335</v>
@@ -23736,10 +23106,10 @@
         <v>46291</v>
       </c>
       <c r="H57" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I57" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J57" s="5" t="s">
         <v>246</v>
@@ -23776,10 +23146,10 @@
         <v>46291</v>
       </c>
       <c r="H58" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I58" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J58" s="5" t="s">
         <v>157</v>
@@ -23814,10 +23184,10 @@
         <v>46291</v>
       </c>
       <c r="H59" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I59" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>313</v>
@@ -23856,10 +23226,10 @@
         <v>46291</v>
       </c>
       <c r="H60" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I60" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J60" s="5" t="s">
         <v>314</v>
@@ -23896,10 +23266,10 @@
         <v>46291</v>
       </c>
       <c r="H61" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I61" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J61" s="5" t="s">
         <v>159</v>
@@ -23934,10 +23304,10 @@
         <v>46291</v>
       </c>
       <c r="H62" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I62" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J62" s="5" t="s">
         <v>27</v>
@@ -23972,10 +23342,10 @@
         <v>46291</v>
       </c>
       <c r="H63" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I63" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J63" s="5" t="s">
         <v>27</v>
@@ -24016,10 +23386,10 @@
         <v>46291</v>
       </c>
       <c r="H64" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I64" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J64" s="5" t="s">
         <v>161</v>
@@ -24056,10 +23426,10 @@
         <v>46291</v>
       </c>
       <c r="H65" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I65" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J65" s="5" t="s">
         <v>320</v>
@@ -24094,10 +23464,10 @@
         <v>46291</v>
       </c>
       <c r="H66" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I66" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J66" s="5" t="s">
         <v>316</v>
@@ -24136,10 +23506,10 @@
         <v>46291</v>
       </c>
       <c r="H67" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I67" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J67" s="5" t="s">
         <v>317</v>
@@ -24174,10 +23544,10 @@
         <v>46291</v>
       </c>
       <c r="H68" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I68" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>321</v>
@@ -24212,10 +23582,10 @@
         <v>46291</v>
       </c>
       <c r="H69" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I69" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>318</v>
@@ -24250,10 +23620,10 @@
         <v>46291</v>
       </c>
       <c r="H70" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I70" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>319</v>
@@ -24288,10 +23658,10 @@
         <v>46291</v>
       </c>
       <c r="H71" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I71" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J71" s="5" t="s">
         <v>337</v>
@@ -24328,10 +23698,10 @@
         <v>46291</v>
       </c>
       <c r="H72" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I72" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>340</v>
@@ -24372,10 +23742,10 @@
         <v>46291</v>
       </c>
       <c r="H73" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I73" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>341</v>
@@ -24412,10 +23782,10 @@
         <v>46291</v>
       </c>
       <c r="H74" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I74" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J74" s="5" t="s">
         <v>323</v>
@@ -24456,10 +23826,10 @@
         <v>46291</v>
       </c>
       <c r="H75" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I75" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J75" s="5" t="s">
         <v>324</v>
@@ -24496,10 +23866,10 @@
         <v>46291</v>
       </c>
       <c r="H76" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I76" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>325</v>
@@ -24540,10 +23910,10 @@
         <v>46291</v>
       </c>
       <c r="H77" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I77" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>326</v>
@@ -24580,10 +23950,10 @@
         <v>46291</v>
       </c>
       <c r="H78" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I78" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J78" s="5" t="s">
         <v>262</v>
@@ -24622,10 +23992,10 @@
         <v>46291</v>
       </c>
       <c r="H79" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I79" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J79" s="5" t="s">
         <v>329</v>
@@ -24660,10 +24030,10 @@
         <v>46291</v>
       </c>
       <c r="H80" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I80" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J80" s="5" t="s">
         <v>330</v>
@@ -24700,10 +24070,10 @@
         <v>46291</v>
       </c>
       <c r="H81" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I81" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J81" s="5" t="s">
         <v>291</v>
@@ -24742,10 +24112,10 @@
         <v>46291</v>
       </c>
       <c r="H82" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I82" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J82" s="5" t="s">
         <v>293</v>
@@ -24780,10 +24150,10 @@
         <v>46291</v>
       </c>
       <c r="H83" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I83" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J83" s="5" t="s">
         <v>294</v>
@@ -24820,10 +24190,10 @@
         <v>46291</v>
       </c>
       <c r="H84" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I84" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J84" s="5" t="s">
         <v>292</v>
@@ -24858,10 +24228,10 @@
         <v>46291</v>
       </c>
       <c r="H85" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I85" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J85" s="5" t="s">
         <v>295</v>
@@ -24896,10 +24266,10 @@
         <v>46291</v>
       </c>
       <c r="H86" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I86" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J86" s="5" t="s">
         <v>296</v>
@@ -24936,10 +24306,10 @@
         <v>46291</v>
       </c>
       <c r="H87" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I87" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J87" s="5" t="s">
         <v>300</v>
@@ -24976,10 +24346,10 @@
         <v>46291</v>
       </c>
       <c r="H88" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I88" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J88" s="5" t="s">
         <v>301</v>
@@ -25014,10 +24384,10 @@
         <v>46291</v>
       </c>
       <c r="H89" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I89" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J89" s="5" t="s">
         <v>298</v>
@@ -25056,10 +24426,10 @@
         <v>46291</v>
       </c>
       <c r="H90" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I90" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J90" s="5" t="s">
         <v>302</v>
@@ -25094,10 +24464,10 @@
         <v>46291</v>
       </c>
       <c r="H91" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I91" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J91" s="5" t="s">
         <v>299</v>
@@ -25132,10 +24502,10 @@
         <v>46291</v>
       </c>
       <c r="H92" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I92" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J92" s="5" t="s">
         <v>187</v>
@@ -25170,10 +24540,10 @@
         <v>46291</v>
       </c>
       <c r="H93" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I93" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J93" s="5" t="s">
         <v>327</v>
@@ -25212,10 +24582,10 @@
         <v>46291</v>
       </c>
       <c r="H94" s="9">
-        <v>0.284722222222222</v>
+        <v>0.28472222222222199</v>
       </c>
       <c r="I94" s="9">
-        <v>0.513888888888889</v>
+        <v>0.51388888888888895</v>
       </c>
       <c r="J94" s="5" t="s">
         <v>328</v>
@@ -25237,32 +24607,9 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="1" orientation="landscape"/>
-  <headerFooter/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="10" max="1048575" man="1"/>
   </colBreaks>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-</worksheet>
 </file>